--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK356"/>
+  <dimension ref="A1:AN356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,21 @@
           <t>odds_match_goals_3.5_under</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>result_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>result_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -747,6 +762,17 @@
       <c r="AK2" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -876,6 +902,17 @@
       <c r="AK3" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1005,6 +1042,17 @@
       <c r="AK4" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1134,6 +1182,17 @@
       <c r="AK5" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1263,6 +1322,17 @@
       <c r="AK6" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1392,6 +1462,17 @@
       <c r="AK7" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1517,6 +1598,17 @@
       <c r="AK8" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1646,6 +1738,17 @@
       <c r="AK9" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1771,6 +1874,17 @@
       <c r="AK10" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1900,6 +2014,17 @@
       <c r="AK11" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2029,6 +2154,17 @@
       <c r="AK12" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2158,6 +2294,17 @@
       <c r="AK13" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2287,6 +2434,13 @@
       <c r="AK14" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2416,6 +2570,13 @@
       <c r="AK15" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2545,6 +2706,13 @@
       <c r="AK16" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2674,6 +2842,13 @@
       <c r="AK17" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2803,6 +2978,13 @@
       <c r="AK18" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2932,6 +3114,13 @@
       <c r="AK19" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -3061,6 +3250,13 @@
       <c r="AK20" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -3190,6 +3386,13 @@
       <c r="AK21" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -3311,6 +3514,13 @@
       <c r="AK22" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -3432,6 +3642,13 @@
       <c r="AK23" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3561,6 +3778,13 @@
       <c r="AK24" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -3686,6 +3910,13 @@
       <c r="AK25" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -3815,6 +4046,13 @@
       <c r="AK26" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -3944,6 +4182,13 @@
       <c r="AK27" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -4073,6 +4318,13 @@
       <c r="AK28" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -4202,6 +4454,13 @@
       <c r="AK29" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -4331,6 +4590,13 @@
       <c r="AK30" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -4452,6 +4718,13 @@
       <c r="AK31" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -4581,6 +4854,13 @@
       <c r="AK32" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -4702,6 +4982,13 @@
       <c r="AK33" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -4830,6 +5117,13 @@
       </c>
       <c r="AK34" t="n">
         <v>1.4</v>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -4936,6 +5230,13 @@
       <c r="AK35" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -5065,6 +5366,13 @@
       <c r="AK36" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -5194,6 +5502,13 @@
       <c r="AK37" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -5323,6 +5638,13 @@
       <c r="AK38" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -5447,6 +5769,13 @@
       </c>
       <c r="AK39" t="n">
         <v>2</v>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5553,6 +5882,13 @@
       <c r="AK40" t="n">
         <v>2</v>
       </c>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -5682,6 +6018,13 @@
       <c r="AK41" t="n">
         <v>2</v>
       </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -5811,6 +6154,13 @@
       <c r="AK42" t="n">
         <v>2</v>
       </c>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -5932,6 +6282,13 @@
       <c r="AK43" t="n">
         <v>2</v>
       </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -6060,6 +6417,13 @@
       </c>
       <c r="AK44" t="n">
         <v>1.44</v>
+      </c>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -6166,6 +6530,13 @@
       <c r="AK45" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -6295,6 +6666,13 @@
       <c r="AK46" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -6424,6 +6802,13 @@
       <c r="AK47" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -6545,6 +6930,13 @@
       <c r="AK48" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -6673,6 +7065,13 @@
       </c>
       <c r="AK49" t="n">
         <v>1.5</v>
+      </c>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -6779,6 +7178,13 @@
       <c r="AK50" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -6900,6 +7306,13 @@
       <c r="AK51" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -7021,6 +7434,13 @@
       <c r="AK52" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -7150,6 +7570,13 @@
       <c r="AK53" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -7271,6 +7698,13 @@
       <c r="AK54" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -7400,6 +7834,13 @@
       <c r="AK55" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -7529,6 +7970,13 @@
       <c r="AK56" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -7658,6 +8106,13 @@
       <c r="AK57" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -7779,6 +8234,13 @@
       <c r="AK58" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -7908,6 +8370,13 @@
       <c r="AK59" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -8037,6 +8506,13 @@
       <c r="AK60" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -8166,6 +8642,13 @@
       <c r="AK61" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -8295,6 +8778,13 @@
       <c r="AK62" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -8420,6 +8910,13 @@
       <c r="AK63" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -8549,6 +9046,13 @@
       <c r="AK64" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -8678,6 +9182,13 @@
       <c r="AK65" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -8807,6 +9318,13 @@
       <c r="AK66" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -8936,6 +9454,13 @@
       <c r="AK67" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -9065,6 +9590,13 @@
       <c r="AK68" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -9194,6 +9726,13 @@
       <c r="AK69" t="n">
         <v>1.57</v>
       </c>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -9323,6 +9862,13 @@
       <c r="AK70" t="n">
         <v>1.57</v>
       </c>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -9452,6 +9998,13 @@
       <c r="AK71" t="n">
         <v>1.57</v>
       </c>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -9581,6 +10134,13 @@
       <c r="AK72" t="n">
         <v>1.57</v>
       </c>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -9702,6 +10262,13 @@
       <c r="AK73" t="n">
         <v>1.57</v>
       </c>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -9823,6 +10390,13 @@
       <c r="AK74" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -9952,6 +10526,13 @@
       <c r="AK75" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -10077,6 +10658,13 @@
       <c r="AK76" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -10206,6 +10794,13 @@
       <c r="AK77" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -10335,6 +10930,13 @@
       <c r="AK78" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -10464,6 +11066,13 @@
       <c r="AK79" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -10593,6 +11202,13 @@
       <c r="AK80" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -10714,6 +11330,13 @@
       <c r="AK81" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -10843,6 +11466,13 @@
       <c r="AK82" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -10972,6 +11602,13 @@
       <c r="AK83" t="n">
         <v>1.62</v>
       </c>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -11096,6 +11733,13 @@
       </c>
       <c r="AK84" t="n">
         <v>2.3</v>
+      </c>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -11202,6 +11846,13 @@
       <c r="AK85" t="n">
         <v>2.3</v>
       </c>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -11323,6 +11974,13 @@
       <c r="AK86" t="n">
         <v>2.3</v>
       </c>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -11448,6 +12106,13 @@
       <c r="AK87" t="n">
         <v>2.3</v>
       </c>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -11573,6 +12238,13 @@
       <c r="AK88" t="n">
         <v>2.3</v>
       </c>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -11694,6 +12366,13 @@
       <c r="AK89" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -11823,6 +12502,13 @@
       <c r="AK90" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -11952,6 +12638,13 @@
       <c r="AK91" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -12081,6 +12774,13 @@
       <c r="AK92" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -12210,6 +12910,13 @@
       <c r="AK93" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -12339,6 +13046,17 @@
       <c r="AK94" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -12468,6 +13186,17 @@
       <c r="AK95" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -12597,6 +13326,17 @@
       <c r="AK96" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -12726,6 +13466,17 @@
       <c r="AK97" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -12855,6 +13606,17 @@
       <c r="AK98" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -12984,6 +13746,17 @@
       <c r="AK99" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -13105,6 +13878,13 @@
       <c r="AK100" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -13234,6 +14014,13 @@
       <c r="AK101" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -13363,6 +14150,13 @@
       <c r="AK102" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -13492,6 +14286,13 @@
       <c r="AK103" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -13617,6 +14418,13 @@
       <c r="AK104" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -13746,6 +14554,17 @@
       <c r="AK105" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -13867,6 +14686,17 @@
       <c r="AK106" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -13996,6 +14826,17 @@
       <c r="AK107" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -14125,6 +14966,17 @@
       <c r="AK108" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -14254,6 +15106,17 @@
       <c r="AK109" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -14383,6 +15246,17 @@
       <c r="AK110" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -14512,6 +15386,17 @@
       <c r="AK111" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -14641,6 +15526,17 @@
       <c r="AK112" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -14770,6 +15666,17 @@
       <c r="AK113" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -14899,6 +15806,17 @@
       <c r="AK114" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -15028,6 +15946,17 @@
       <c r="AK115" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -15149,6 +16078,17 @@
       <c r="AK116" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -15278,6 +16218,17 @@
       <c r="AK117" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -15407,6 +16358,17 @@
       <c r="AK118" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -15536,6 +16498,17 @@
       <c r="AK119" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -15665,6 +16638,17 @@
       <c r="AK120" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -15794,6 +16778,17 @@
       <c r="AK121" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -15923,6 +16918,17 @@
       <c r="AK122" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -16052,6 +17058,17 @@
       <c r="AK123" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -16181,6 +17198,17 @@
       <c r="AK124" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN124" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -16310,6 +17338,17 @@
       <c r="AK125" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN125" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -16439,6 +17478,17 @@
       <c r="AK126" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -16568,6 +17618,17 @@
       <c r="AK127" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -16697,6 +17758,17 @@
       <c r="AK128" t="n">
         <v>1.14</v>
       </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN128" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -16818,6 +17890,17 @@
       <c r="AK129" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN129" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -16947,6 +18030,17 @@
       <c r="AK130" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN130" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -17068,6 +18162,17 @@
       <c r="AK131" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN131" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -17197,6 +18302,17 @@
       <c r="AK132" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -17326,6 +18442,17 @@
       <c r="AK133" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN133" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -17455,6 +18582,17 @@
       <c r="AK134" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -17584,6 +18722,17 @@
       <c r="AK135" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN135" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -17713,6 +18862,17 @@
       <c r="AK136" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -17842,6 +19002,17 @@
       <c r="AK137" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN137" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -17971,6 +19142,17 @@
       <c r="AK138" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -18100,6 +19282,17 @@
       <c r="AK139" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN139" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -18229,6 +19422,17 @@
       <c r="AK140" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN140" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -18358,6 +19562,13 @@
       <c r="AK141" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL141" t="inlineStr"/>
+      <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -18487,6 +19698,13 @@
       <c r="AK142" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -18616,6 +19834,13 @@
       <c r="AK143" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -18745,6 +19970,13 @@
       <c r="AK144" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -18874,6 +20106,13 @@
       <c r="AK145" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -18995,6 +20234,13 @@
       <c r="AK146" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -19116,6 +20362,13 @@
       <c r="AK147" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -19245,6 +20498,13 @@
       <c r="AK148" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -19374,6 +20634,13 @@
       <c r="AK149" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -19503,6 +20770,13 @@
       <c r="AK150" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -19632,6 +20906,13 @@
       <c r="AK151" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -19761,6 +21042,13 @@
       <c r="AK152" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -19890,6 +21178,13 @@
       <c r="AK153" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -20019,6 +21314,13 @@
       <c r="AK154" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -20148,6 +21450,13 @@
       <c r="AK155" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL155" t="inlineStr"/>
+      <c r="AM155" t="inlineStr"/>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -20277,6 +21586,13 @@
       <c r="AK156" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL156" t="inlineStr"/>
+      <c r="AM156" t="inlineStr"/>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -20406,6 +21722,13 @@
       <c r="AK157" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL157" t="inlineStr"/>
+      <c r="AM157" t="inlineStr"/>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -20535,6 +21858,13 @@
       <c r="AK158" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL158" t="inlineStr"/>
+      <c r="AM158" t="inlineStr"/>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -20664,6 +21994,13 @@
       <c r="AK159" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL159" t="inlineStr"/>
+      <c r="AM159" t="inlineStr"/>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -20793,6 +22130,13 @@
       <c r="AK160" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -20922,6 +22266,13 @@
       <c r="AK161" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -21051,6 +22402,13 @@
       <c r="AK162" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL162" t="inlineStr"/>
+      <c r="AM162" t="inlineStr"/>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -21180,6 +22538,13 @@
       <c r="AK163" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL163" t="inlineStr"/>
+      <c r="AM163" t="inlineStr"/>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -21309,6 +22674,13 @@
       <c r="AK164" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -21438,6 +22810,13 @@
       <c r="AK165" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -21567,6 +22946,13 @@
       <c r="AK166" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -21696,6 +23082,13 @@
       <c r="AK167" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -21825,6 +23218,13 @@
       <c r="AK168" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL168" t="inlineStr"/>
+      <c r="AM168" t="inlineStr"/>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -21954,6 +23354,13 @@
       <c r="AK169" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL169" t="inlineStr"/>
+      <c r="AM169" t="inlineStr"/>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -22075,6 +23482,13 @@
       <c r="AK170" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL170" t="inlineStr"/>
+      <c r="AM170" t="inlineStr"/>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -22196,6 +23610,13 @@
       <c r="AK171" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL171" t="inlineStr"/>
+      <c r="AM171" t="inlineStr"/>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -22317,6 +23738,13 @@
       <c r="AK172" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL172" t="inlineStr"/>
+      <c r="AM172" t="inlineStr"/>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -22446,6 +23874,13 @@
       <c r="AK173" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL173" t="inlineStr"/>
+      <c r="AM173" t="inlineStr"/>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -22567,6 +24002,13 @@
       <c r="AK174" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL174" t="inlineStr"/>
+      <c r="AM174" t="inlineStr"/>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -22688,6 +24130,13 @@
       <c r="AK175" t="n">
         <v>1.5</v>
       </c>
+      <c r="AL175" t="inlineStr"/>
+      <c r="AM175" t="inlineStr"/>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -22817,6 +24266,13 @@
       <c r="AK176" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -22946,6 +24402,13 @@
       <c r="AK177" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -23075,6 +24538,13 @@
       <c r="AK178" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -23204,6 +24674,13 @@
       <c r="AK179" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -23333,6 +24810,13 @@
       <c r="AK180" t="n">
         <v>1.4</v>
       </c>
+      <c r="AL180" t="inlineStr"/>
+      <c r="AM180" t="inlineStr"/>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -23457,6 +24941,13 @@
       </c>
       <c r="AK181" t="n">
         <v>1.67</v>
+      </c>
+      <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -23563,6 +25054,13 @@
       <c r="AK182" t="n">
         <v>1.67</v>
       </c>
+      <c r="AL182" t="inlineStr"/>
+      <c r="AM182" t="inlineStr"/>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -23692,6 +25190,13 @@
       <c r="AK183" t="n">
         <v>1.67</v>
       </c>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -23813,6 +25318,13 @@
       <c r="AK184" t="n">
         <v>1.67</v>
       </c>
+      <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -23942,6 +25454,13 @@
       <c r="AK185" t="n">
         <v>1.67</v>
       </c>
+      <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -24067,6 +25586,13 @@
       <c r="AK186" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL186" t="inlineStr"/>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -24196,6 +25722,13 @@
       <c r="AK187" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -24325,6 +25858,13 @@
       <c r="AK188" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -24454,6 +25994,13 @@
       <c r="AK189" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL189" t="inlineStr"/>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -24575,6 +26122,13 @@
       <c r="AK190" t="n">
         <v>1.73</v>
       </c>
+      <c r="AL190" t="inlineStr"/>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -24704,6 +26258,13 @@
       <c r="AK191" t="n">
         <v>1.53</v>
       </c>
+      <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -24825,6 +26386,13 @@
       <c r="AK192" t="n">
         <v>1.53</v>
       </c>
+      <c r="AL192" t="inlineStr"/>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -24954,6 +26522,13 @@
       <c r="AK193" t="n">
         <v>1.53</v>
       </c>
+      <c r="AL193" t="inlineStr"/>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -25083,6 +26658,13 @@
       <c r="AK194" t="n">
         <v>1.53</v>
       </c>
+      <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -25204,6 +26786,13 @@
       <c r="AK195" t="n">
         <v>1.53</v>
       </c>
+      <c r="AL195" t="inlineStr"/>
+      <c r="AM195" t="inlineStr"/>
+      <c r="AN195" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -25332,6 +26921,13 @@
       </c>
       <c r="AK196" t="n">
         <v>1.44</v>
+      </c>
+      <c r="AL196" t="inlineStr"/>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -25438,6 +27034,13 @@
       <c r="AK197" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL197" t="inlineStr"/>
+      <c r="AM197" t="inlineStr"/>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -25567,6 +27170,13 @@
       <c r="AK198" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL198" t="inlineStr"/>
+      <c r="AM198" t="inlineStr"/>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -25696,6 +27306,13 @@
       <c r="AK199" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL199" t="inlineStr"/>
+      <c r="AM199" t="inlineStr"/>
+      <c r="AN199" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -25821,6 +27438,13 @@
       <c r="AK200" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL200" t="inlineStr"/>
+      <c r="AM200" t="inlineStr"/>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -25946,6 +27570,13 @@
       <c r="AK201" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL201" t="inlineStr"/>
+      <c r="AM201" t="inlineStr"/>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -26075,6 +27706,13 @@
       <c r="AK202" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL202" t="inlineStr"/>
+      <c r="AM202" t="inlineStr"/>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -26204,6 +27842,13 @@
       <c r="AK203" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL203" t="inlineStr"/>
+      <c r="AM203" t="inlineStr"/>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -26333,6 +27978,13 @@
       <c r="AK204" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL204" t="inlineStr"/>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -26462,6 +28114,13 @@
       <c r="AK205" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL205" t="inlineStr"/>
+      <c r="AM205" t="inlineStr"/>
+      <c r="AN205" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -26591,6 +28250,13 @@
       <c r="AK206" t="n">
         <v>1.36</v>
       </c>
+      <c r="AL206" t="inlineStr"/>
+      <c r="AM206" t="inlineStr"/>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -26720,6 +28386,13 @@
       <c r="AK207" t="n">
         <v>1.36</v>
       </c>
+      <c r="AL207" t="inlineStr"/>
+      <c r="AM207" t="inlineStr"/>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -26849,6 +28522,13 @@
       <c r="AK208" t="n">
         <v>1.36</v>
       </c>
+      <c r="AL208" t="inlineStr"/>
+      <c r="AM208" t="inlineStr"/>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -26978,6 +28658,13 @@
       <c r="AK209" t="n">
         <v>1.36</v>
       </c>
+      <c r="AL209" t="inlineStr"/>
+      <c r="AM209" t="inlineStr"/>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -27107,6 +28794,13 @@
       <c r="AK210" t="n">
         <v>1.36</v>
       </c>
+      <c r="AL210" t="inlineStr"/>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -27236,6 +28930,13 @@
       <c r="AK211" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL211" t="inlineStr"/>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -27357,6 +29058,13 @@
       <c r="AK212" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -27486,6 +29194,13 @@
       <c r="AK213" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL213" t="inlineStr"/>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -27615,6 +29330,13 @@
       <c r="AK214" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL214" t="inlineStr"/>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -27744,6 +29466,13 @@
       <c r="AK215" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -27872,6 +29601,13 @@
       </c>
       <c r="AK216" t="n">
         <v>1.44</v>
+      </c>
+      <c r="AL216" t="inlineStr"/>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -27978,6 +29714,13 @@
       <c r="AK217" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL217" t="inlineStr"/>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -28107,6 +29850,13 @@
       <c r="AK218" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL218" t="inlineStr"/>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -28228,6 +29978,13 @@
       <c r="AK219" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL219" t="inlineStr"/>
+      <c r="AM219" t="inlineStr"/>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -28349,6 +30106,13 @@
       <c r="AK220" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL220" t="inlineStr"/>
+      <c r="AM220" t="inlineStr"/>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -28478,6 +30242,13 @@
       <c r="AK221" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL221" t="inlineStr"/>
+      <c r="AM221" t="inlineStr"/>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -28607,6 +30378,13 @@
       <c r="AK222" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL222" t="inlineStr"/>
+      <c r="AM222" t="inlineStr"/>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -28736,6 +30514,13 @@
       <c r="AK223" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -28865,6 +30650,13 @@
       <c r="AK224" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -28994,6 +30786,13 @@
       <c r="AK225" t="n">
         <v>1.29</v>
       </c>
+      <c r="AL225" t="inlineStr"/>
+      <c r="AM225" t="inlineStr"/>
+      <c r="AN225" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -29123,6 +30922,13 @@
       <c r="AK226" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
+      <c r="AN226" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -29252,6 +31058,13 @@
       <c r="AK227" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL227" t="inlineStr"/>
+      <c r="AM227" t="inlineStr"/>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -29381,6 +31194,13 @@
       <c r="AK228" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL228" t="inlineStr"/>
+      <c r="AM228" t="inlineStr"/>
+      <c r="AN228" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -29510,6 +31330,13 @@
       <c r="AK229" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL229" t="inlineStr"/>
+      <c r="AM229" t="inlineStr"/>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -29639,6 +31466,13 @@
       <c r="AK230" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL230" t="inlineStr"/>
+      <c r="AM230" t="inlineStr"/>
+      <c r="AN230" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -29768,6 +31602,17 @@
       <c r="AK231" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -29897,6 +31742,17 @@
       <c r="AK232" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN232" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -30026,6 +31882,17 @@
       <c r="AK233" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN233" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -30155,6 +32022,17 @@
       <c r="AK234" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN234" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -30284,6 +32162,17 @@
       <c r="AK235" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN235" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -30413,6 +32302,17 @@
       <c r="AK236" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN236" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -30542,6 +32442,17 @@
       <c r="AK237" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN237" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -30671,6 +32582,17 @@
       <c r="AK238" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN238" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -30800,6 +32722,17 @@
       <c r="AK239" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN239" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -30929,6 +32862,17 @@
       <c r="AK240" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN240" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -31058,6 +33002,17 @@
       <c r="AK241" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN241" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -31187,6 +33142,17 @@
       <c r="AK242" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -31316,6 +33282,17 @@
       <c r="AK243" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN243" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -31437,6 +33414,17 @@
       <c r="AK244" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN244" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -31566,6 +33554,17 @@
       <c r="AK245" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -31687,6 +33686,17 @@
       <c r="AK246" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -31808,6 +33818,17 @@
       <c r="AK247" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -31937,6 +33958,17 @@
       <c r="AK248" t="n">
         <v>1.3</v>
       </c>
+      <c r="AL248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -32066,6 +34098,17 @@
       <c r="AK249" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -32187,6 +34230,17 @@
       <c r="AK250" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -32316,6 +34370,17 @@
       <c r="AK251" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN251" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -32445,6 +34510,17 @@
       <c r="AK252" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -32574,6 +34650,17 @@
       <c r="AK253" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN253" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -32695,6 +34782,17 @@
       <c r="AK254" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN254" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -32824,6 +34922,17 @@
       <c r="AK255" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN255" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -32953,6 +35062,17 @@
       <c r="AK256" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN256" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -33082,6 +35202,17 @@
       <c r="AK257" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN257" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -33203,6 +35334,17 @@
       <c r="AK258" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN258" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -33332,6 +35474,17 @@
       <c r="AK259" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN259" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -33461,6 +35614,17 @@
       <c r="AK260" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN260" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -33590,6 +35754,17 @@
       <c r="AK261" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN261" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -33711,6 +35886,17 @@
       <c r="AK262" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN262" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -33840,6 +36026,17 @@
       <c r="AK263" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN263" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -33965,6 +36162,17 @@
       <c r="AK264" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN264" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -34094,6 +36302,17 @@
       <c r="AK265" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN265" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -34223,6 +36442,17 @@
       <c r="AK266" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN266" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -34344,6 +36574,17 @@
       <c r="AK267" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN267" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -34473,6 +36714,17 @@
       <c r="AK268" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN268" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -34594,6 +36846,17 @@
       <c r="AK269" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN269" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -34723,6 +36986,17 @@
       <c r="AK270" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN270" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -34852,6 +37126,17 @@
       <c r="AK271" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN271" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -34981,6 +37266,17 @@
       <c r="AK272" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN272" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -35110,6 +37406,17 @@
       <c r="AK273" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN273" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -35239,6 +37546,17 @@
       <c r="AK274" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN274" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -35368,6 +37686,17 @@
       <c r="AK275" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN275" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -35497,6 +37826,17 @@
       <c r="AK276" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN276" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -35626,6 +37966,17 @@
       <c r="AK277" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN277" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -35755,6 +38106,17 @@
       <c r="AK278" t="n">
         <v>1.33</v>
       </c>
+      <c r="AL278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN278" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -35884,6 +38246,13 @@
       <c r="AK279" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL279" t="inlineStr"/>
+      <c r="AM279" t="inlineStr"/>
+      <c r="AN279" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -36013,6 +38382,13 @@
       <c r="AK280" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL280" t="inlineStr"/>
+      <c r="AM280" t="inlineStr"/>
+      <c r="AN280" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -36142,6 +38518,13 @@
       <c r="AK281" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL281" t="inlineStr"/>
+      <c r="AM281" t="inlineStr"/>
+      <c r="AN281" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -36271,6 +38654,13 @@
       <c r="AK282" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL282" t="inlineStr"/>
+      <c r="AM282" t="inlineStr"/>
+      <c r="AN282" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -36392,6 +38782,13 @@
       <c r="AK283" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL283" t="inlineStr"/>
+      <c r="AM283" t="inlineStr"/>
+      <c r="AN283" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -36521,6 +38918,13 @@
       <c r="AK284" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL284" t="inlineStr"/>
+      <c r="AM284" t="inlineStr"/>
+      <c r="AN284" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -36650,6 +39054,13 @@
       <c r="AK285" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr"/>
+      <c r="AN285" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -36779,6 +39190,13 @@
       <c r="AK286" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr"/>
+      <c r="AN286" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -36908,6 +39326,13 @@
       <c r="AK287" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
+      <c r="AN287" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -37037,6 +39462,13 @@
       <c r="AK288" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL288" t="inlineStr"/>
+      <c r="AM288" t="inlineStr"/>
+      <c r="AN288" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -37166,6 +39598,13 @@
       <c r="AK289" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL289" t="inlineStr"/>
+      <c r="AM289" t="inlineStr"/>
+      <c r="AN289" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -37287,6 +39726,13 @@
       <c r="AK290" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
+      <c r="AN290" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -37408,6 +39854,13 @@
       <c r="AK291" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL291" t="inlineStr"/>
+      <c r="AM291" t="inlineStr"/>
+      <c r="AN291" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -37537,6 +39990,13 @@
       <c r="AK292" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL292" t="inlineStr"/>
+      <c r="AM292" t="inlineStr"/>
+      <c r="AN292" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -37658,6 +40118,13 @@
       <c r="AK293" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL293" t="inlineStr"/>
+      <c r="AM293" t="inlineStr"/>
+      <c r="AN293" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -37787,6 +40254,13 @@
       <c r="AK294" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL294" t="inlineStr"/>
+      <c r="AM294" t="inlineStr"/>
+      <c r="AN294" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -37916,6 +40390,13 @@
       <c r="AK295" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL295" t="inlineStr"/>
+      <c r="AM295" t="inlineStr"/>
+      <c r="AN295" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -38037,6 +40518,13 @@
       <c r="AK296" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL296" t="inlineStr"/>
+      <c r="AM296" t="inlineStr"/>
+      <c r="AN296" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -38166,6 +40654,13 @@
       <c r="AK297" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL297" t="inlineStr"/>
+      <c r="AM297" t="inlineStr"/>
+      <c r="AN297" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -38295,6 +40790,13 @@
       <c r="AK298" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL298" t="inlineStr"/>
+      <c r="AM298" t="inlineStr"/>
+      <c r="AN298" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -38424,6 +40926,13 @@
       <c r="AK299" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL299" t="inlineStr"/>
+      <c r="AM299" t="inlineStr"/>
+      <c r="AN299" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -38549,6 +41058,13 @@
       <c r="AK300" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL300" t="inlineStr"/>
+      <c r="AM300" t="inlineStr"/>
+      <c r="AN300" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -38678,6 +41194,13 @@
       <c r="AK301" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL301" t="inlineStr"/>
+      <c r="AM301" t="inlineStr"/>
+      <c r="AN301" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -38807,6 +41330,13 @@
       <c r="AK302" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL302" t="inlineStr"/>
+      <c r="AM302" t="inlineStr"/>
+      <c r="AN302" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -38936,6 +41466,13 @@
       <c r="AK303" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL303" t="inlineStr"/>
+      <c r="AM303" t="inlineStr"/>
+      <c r="AN303" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -39065,6 +41602,13 @@
       <c r="AK304" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL304" t="inlineStr"/>
+      <c r="AM304" t="inlineStr"/>
+      <c r="AN304" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -39194,6 +41738,13 @@
       <c r="AK305" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL305" t="inlineStr"/>
+      <c r="AM305" t="inlineStr"/>
+      <c r="AN305" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -39323,6 +41874,13 @@
       <c r="AK306" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL306" t="inlineStr"/>
+      <c r="AM306" t="inlineStr"/>
+      <c r="AN306" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -39444,6 +42002,13 @@
       <c r="AK307" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL307" t="inlineStr"/>
+      <c r="AM307" t="inlineStr"/>
+      <c r="AN307" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -39573,6 +42138,13 @@
       <c r="AK308" t="n">
         <v>1.12</v>
       </c>
+      <c r="AL308" t="inlineStr"/>
+      <c r="AM308" t="inlineStr"/>
+      <c r="AN308" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -39702,6 +42274,13 @@
       <c r="AK309" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL309" t="inlineStr"/>
+      <c r="AM309" t="inlineStr"/>
+      <c r="AN309" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -39831,6 +42410,13 @@
       <c r="AK310" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL310" t="inlineStr"/>
+      <c r="AM310" t="inlineStr"/>
+      <c r="AN310" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -39960,6 +42546,13 @@
       <c r="AK311" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL311" t="inlineStr"/>
+      <c r="AM311" t="inlineStr"/>
+      <c r="AN311" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -40089,6 +42682,13 @@
       <c r="AK312" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL312" t="inlineStr"/>
+      <c r="AM312" t="inlineStr"/>
+      <c r="AN312" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -40218,6 +42818,13 @@
       <c r="AK313" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL313" t="inlineStr"/>
+      <c r="AM313" t="inlineStr"/>
+      <c r="AN313" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -40339,6 +42946,13 @@
       <c r="AK314" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL314" t="inlineStr"/>
+      <c r="AM314" t="inlineStr"/>
+      <c r="AN314" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -40468,6 +43082,13 @@
       <c r="AK315" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL315" t="inlineStr"/>
+      <c r="AM315" t="inlineStr"/>
+      <c r="AN315" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -40597,6 +43218,13 @@
       <c r="AK316" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL316" t="inlineStr"/>
+      <c r="AM316" t="inlineStr"/>
+      <c r="AN316" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -40726,6 +43354,13 @@
       <c r="AK317" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL317" t="inlineStr"/>
+      <c r="AM317" t="inlineStr"/>
+      <c r="AN317" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -40855,6 +43490,13 @@
       <c r="AK318" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL318" t="inlineStr"/>
+      <c r="AM318" t="inlineStr"/>
+      <c r="AN318" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -40984,6 +43626,13 @@
       <c r="AK319" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL319" t="inlineStr"/>
+      <c r="AM319" t="inlineStr"/>
+      <c r="AN319" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -41105,6 +43754,13 @@
       <c r="AK320" t="n">
         <v>1.25</v>
       </c>
+      <c r="AL320" t="inlineStr"/>
+      <c r="AM320" t="inlineStr"/>
+      <c r="AN320" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -41234,6 +43890,13 @@
       <c r="AK321" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL321" t="inlineStr"/>
+      <c r="AM321" t="inlineStr"/>
+      <c r="AN321" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -41363,6 +44026,13 @@
       <c r="AK322" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL322" t="inlineStr"/>
+      <c r="AM322" t="inlineStr"/>
+      <c r="AN322" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -41492,6 +44162,13 @@
       <c r="AK323" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL323" t="inlineStr"/>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -41617,6 +44294,13 @@
       <c r="AK324" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL324" t="inlineStr"/>
+      <c r="AM324" t="inlineStr"/>
+      <c r="AN324" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -41746,6 +44430,13 @@
       <c r="AK325" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL325" t="inlineStr"/>
+      <c r="AM325" t="inlineStr"/>
+      <c r="AN325" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -41875,6 +44566,13 @@
       <c r="AK326" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL326" t="inlineStr"/>
+      <c r="AM326" t="inlineStr"/>
+      <c r="AN326" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -42004,6 +44702,13 @@
       <c r="AK327" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL327" t="inlineStr"/>
+      <c r="AM327" t="inlineStr"/>
+      <c r="AN327" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -42133,6 +44838,13 @@
       <c r="AK328" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL328" t="inlineStr"/>
+      <c r="AM328" t="inlineStr"/>
+      <c r="AN328" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -42262,6 +44974,13 @@
       <c r="AK329" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL329" t="inlineStr"/>
+      <c r="AM329" t="inlineStr"/>
+      <c r="AN329" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -42391,6 +45110,13 @@
       <c r="AK330" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL330" t="inlineStr"/>
+      <c r="AM330" t="inlineStr"/>
+      <c r="AN330" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -42520,6 +45246,13 @@
       <c r="AK331" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL331" t="inlineStr"/>
+      <c r="AM331" t="inlineStr"/>
+      <c r="AN331" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -42649,6 +45382,13 @@
       <c r="AK332" t="n">
         <v>1.18</v>
       </c>
+      <c r="AL332" t="inlineStr"/>
+      <c r="AM332" t="inlineStr"/>
+      <c r="AN332" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -42770,6 +45510,13 @@
       <c r="AK333" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL333" t="inlineStr"/>
+      <c r="AM333" t="inlineStr"/>
+      <c r="AN333" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -42899,6 +45646,13 @@
       <c r="AK334" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL334" t="inlineStr"/>
+      <c r="AM334" t="inlineStr"/>
+      <c r="AN334" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -43020,6 +45774,13 @@
       <c r="AK335" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL335" t="inlineStr"/>
+      <c r="AM335" t="inlineStr"/>
+      <c r="AN335" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -43149,6 +45910,13 @@
       <c r="AK336" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL336" t="inlineStr"/>
+      <c r="AM336" t="inlineStr"/>
+      <c r="AN336" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -43278,6 +46046,13 @@
       <c r="AK337" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL337" t="inlineStr"/>
+      <c r="AM337" t="inlineStr"/>
+      <c r="AN337" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -43407,6 +46182,13 @@
       <c r="AK338" t="n">
         <v>1.22</v>
       </c>
+      <c r="AL338" t="inlineStr"/>
+      <c r="AM338" t="inlineStr"/>
+      <c r="AN338" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -43536,6 +46318,13 @@
       <c r="AK339" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL339" t="inlineStr"/>
+      <c r="AM339" t="inlineStr"/>
+      <c r="AN339" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -43665,6 +46454,13 @@
       <c r="AK340" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL340" t="inlineStr"/>
+      <c r="AM340" t="inlineStr"/>
+      <c r="AN340" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -43794,6 +46590,13 @@
       <c r="AK341" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL341" t="inlineStr"/>
+      <c r="AM341" t="inlineStr"/>
+      <c r="AN341" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -43923,6 +46726,13 @@
       <c r="AK342" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL342" t="inlineStr"/>
+      <c r="AM342" t="inlineStr"/>
+      <c r="AN342" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -44052,6 +46862,13 @@
       <c r="AK343" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL343" t="inlineStr"/>
+      <c r="AM343" t="inlineStr"/>
+      <c r="AN343" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -44181,6 +46998,13 @@
       <c r="AK344" t="n">
         <v>1.17</v>
       </c>
+      <c r="AL344" t="inlineStr"/>
+      <c r="AM344" t="inlineStr"/>
+      <c r="AN344" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -44310,6 +47134,13 @@
       <c r="AK345" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL345" t="inlineStr"/>
+      <c r="AM345" t="inlineStr"/>
+      <c r="AN345" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -44439,6 +47270,13 @@
       <c r="AK346" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL346" t="inlineStr"/>
+      <c r="AM346" t="inlineStr"/>
+      <c r="AN346" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -44568,6 +47406,13 @@
       <c r="AK347" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL347" t="inlineStr"/>
+      <c r="AM347" t="inlineStr"/>
+      <c r="AN347" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -44693,6 +47538,13 @@
       <c r="AK348" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -44822,6 +47674,13 @@
       <c r="AK349" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL349" t="inlineStr"/>
+      <c r="AM349" t="inlineStr"/>
+      <c r="AN349" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -44951,6 +47810,13 @@
       <c r="AK350" t="n">
         <v>1.2</v>
       </c>
+      <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
+      <c r="AN350" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -45080,6 +47946,13 @@
       <c r="AK351" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL351" t="inlineStr"/>
+      <c r="AM351" t="inlineStr"/>
+      <c r="AN351" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -45209,6 +48082,13 @@
       <c r="AK352" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL352" t="inlineStr"/>
+      <c r="AM352" t="inlineStr"/>
+      <c r="AN352" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -45338,6 +48218,13 @@
       <c r="AK353" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
+      <c r="AN353" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -45467,6 +48354,13 @@
       <c r="AK354" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL354" t="inlineStr"/>
+      <c r="AM354" t="inlineStr"/>
+      <c r="AN354" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -45596,6 +48490,13 @@
       <c r="AK355" t="n">
         <v>1.44</v>
       </c>
+      <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
+      <c r="AN355" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -45716,6 +48617,13 @@
       </c>
       <c r="AK356" t="n">
         <v>1.44</v>
+      </c>
+      <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
+      <c r="AN356" t="inlineStr">
+        <is>
+          <t>nostarted</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -2434,11 +2434,15 @@
       <c r="AK14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2</v>
+      </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2570,11 +2574,15 @@
       <c r="AK15" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2</v>
+      </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2706,11 +2714,15 @@
       <c r="AK16" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2</v>
+      </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2842,11 +2854,15 @@
       <c r="AK17" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2</v>
+      </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2978,11 +2994,15 @@
       <c r="AK18" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2</v>
+      </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3114,11 +3134,15 @@
       <c r="AK19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2</v>
+      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3250,11 +3274,15 @@
       <c r="AK20" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2</v>
+      </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3386,11 +3414,15 @@
       <c r="AK21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2</v>
+      </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3514,11 +3546,15 @@
       <c r="AK22" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2</v>
+      </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3642,11 +3678,15 @@
       <c r="AK23" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>2</v>
+      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3778,11 +3818,15 @@
       <c r="AK24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>3</v>
+      </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3910,11 +3954,15 @@
       <c r="AK25" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>3</v>
+      </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4046,11 +4094,15 @@
       <c r="AK26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>3</v>
+      </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4182,11 +4234,15 @@
       <c r="AK27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>3</v>
+      </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4318,11 +4374,15 @@
       <c r="AK28" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>3</v>
+      </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4454,11 +4514,15 @@
       <c r="AK29" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4590,11 +4654,15 @@
       <c r="AK30" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4718,11 +4786,15 @@
       <c r="AK31" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4854,11 +4926,15 @@
       <c r="AK32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4982,11 +5058,15 @@
       <c r="AK33" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5118,11 +5198,15 @@
       <c r="AK34" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5230,11 +5314,15 @@
       <c r="AK35" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5366,11 +5454,15 @@
       <c r="AK36" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5502,11 +5594,15 @@
       <c r="AK37" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5638,11 +5734,15 @@
       <c r="AK38" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5770,11 +5870,15 @@
       <c r="AK39" t="n">
         <v>2</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5882,11 +5986,15 @@
       <c r="AK40" t="n">
         <v>2</v>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1</v>
+      </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6018,11 +6126,15 @@
       <c r="AK41" t="n">
         <v>2</v>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1</v>
+      </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6154,11 +6266,15 @@
       <c r="AK42" t="n">
         <v>2</v>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1</v>
+      </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6282,11 +6398,15 @@
       <c r="AK43" t="n">
         <v>2</v>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1</v>
+      </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6418,11 +6538,15 @@
       <c r="AK44" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1</v>
+      </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6530,11 +6654,15 @@
       <c r="AK45" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AL45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1</v>
+      </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6666,11 +6794,15 @@
       <c r="AK46" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6802,11 +6934,15 @@
       <c r="AK47" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6930,11 +7066,15 @@
       <c r="AK48" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
+      <c r="AL48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7066,11 +7206,15 @@
       <c r="AK49" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
+      <c r="AL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7178,11 +7322,15 @@
       <c r="AK50" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
+      <c r="AL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7306,11 +7454,15 @@
       <c r="AK51" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
+      <c r="AL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7434,11 +7586,15 @@
       <c r="AK52" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
+      <c r="AL52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7570,11 +7726,15 @@
       <c r="AK53" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
+      <c r="AL53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7698,11 +7858,15 @@
       <c r="AK54" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7834,11 +7998,15 @@
       <c r="AK55" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7970,11 +8138,15 @@
       <c r="AK56" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8106,11 +8278,15 @@
       <c r="AK57" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8234,11 +8410,15 @@
       <c r="AK58" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8370,11 +8550,15 @@
       <c r="AK59" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8506,11 +8690,15 @@
       <c r="AK60" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
+      <c r="AL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8642,11 +8830,15 @@
       <c r="AK61" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8778,11 +8970,15 @@
       <c r="AK62" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8910,11 +9106,15 @@
       <c r="AK63" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9046,11 +9246,15 @@
       <c r="AK64" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1</v>
+      </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9182,11 +9386,15 @@
       <c r="AK65" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1</v>
+      </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9318,11 +9526,15 @@
       <c r="AK66" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1</v>
+      </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9454,11 +9666,15 @@
       <c r="AK67" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1</v>
+      </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9590,11 +9806,15 @@
       <c r="AK68" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1</v>
+      </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9726,11 +9946,15 @@
       <c r="AK69" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
+      <c r="AL69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1</v>
+      </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9862,11 +10086,15 @@
       <c r="AK70" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
+      <c r="AL70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1</v>
+      </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9998,11 +10226,15 @@
       <c r="AK71" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
+      <c r="AL71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1</v>
+      </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10134,11 +10366,15 @@
       <c r="AK72" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
+      <c r="AL72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1</v>
+      </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10262,11 +10498,15 @@
       <c r="AK73" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
+      <c r="AL73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1</v>
+      </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10390,11 +10630,15 @@
       <c r="AK74" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1</v>
+      </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10526,11 +10770,15 @@
       <c r="AK75" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1</v>
+      </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10658,11 +10906,15 @@
       <c r="AK76" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1</v>
+      </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10794,11 +11046,15 @@
       <c r="AK77" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
+      <c r="AL77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1</v>
+      </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10930,11 +11186,15 @@
       <c r="AK78" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
+      <c r="AL78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1</v>
+      </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11066,11 +11326,15 @@
       <c r="AK79" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
+      <c r="AL79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1</v>
+      </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11202,11 +11466,15 @@
       <c r="AK80" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
+      <c r="AL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1</v>
+      </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11330,11 +11598,15 @@
       <c r="AK81" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
+      <c r="AL81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1</v>
+      </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11466,11 +11738,15 @@
       <c r="AK82" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr"/>
+      <c r="AL82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1</v>
+      </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11602,11 +11878,15 @@
       <c r="AK83" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1</v>
+      </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11734,11 +12014,15 @@
       <c r="AK84" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr"/>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>3</v>
+      </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11846,11 +12130,15 @@
       <c r="AK85" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="inlineStr"/>
+      <c r="AL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>3</v>
+      </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11974,11 +12262,15 @@
       <c r="AK86" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="inlineStr"/>
+      <c r="AL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>3</v>
+      </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12106,11 +12398,15 @@
       <c r="AK87" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr"/>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>3</v>
+      </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12238,11 +12534,15 @@
       <c r="AK88" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="inlineStr"/>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>3</v>
+      </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12366,11 +12666,15 @@
       <c r="AK89" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
+      <c r="AL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1</v>
+      </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12502,11 +12806,15 @@
       <c r="AK90" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="inlineStr"/>
+      <c r="AL90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1</v>
+      </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12638,11 +12946,15 @@
       <c r="AK91" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="inlineStr"/>
+      <c r="AL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1</v>
+      </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12774,11 +13086,15 @@
       <c r="AK92" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="inlineStr"/>
+      <c r="AL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1</v>
+      </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12910,11 +13226,15 @@
       <c r="AK93" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr"/>
+      <c r="AL93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1</v>
+      </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13878,11 +14198,15 @@
       <c r="AK100" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="inlineStr"/>
+      <c r="AL100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1</v>
+      </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14014,11 +14338,15 @@
       <c r="AK101" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="inlineStr"/>
+      <c r="AL101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1</v>
+      </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14150,11 +14478,15 @@
       <c r="AK102" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="inlineStr"/>
+      <c r="AL102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1</v>
+      </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14286,11 +14618,15 @@
       <c r="AK103" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
+      <c r="AL103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1</v>
+      </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14418,11 +14754,15 @@
       <c r="AK104" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="inlineStr"/>
+      <c r="AL104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1</v>
+      </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19562,11 +19902,15 @@
       <c r="AK141" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL141" t="inlineStr"/>
-      <c r="AM141" t="inlineStr"/>
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1</v>
+      </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19698,11 +20042,15 @@
       <c r="AK142" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL142" t="inlineStr"/>
-      <c r="AM142" t="inlineStr"/>
+      <c r="AL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1</v>
+      </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19834,11 +20182,15 @@
       <c r="AK143" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL143" t="inlineStr"/>
-      <c r="AM143" t="inlineStr"/>
+      <c r="AL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1</v>
+      </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19970,11 +20322,15 @@
       <c r="AK144" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL144" t="inlineStr"/>
-      <c r="AM144" t="inlineStr"/>
+      <c r="AL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1</v>
+      </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20106,11 +20462,15 @@
       <c r="AK145" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL145" t="inlineStr"/>
-      <c r="AM145" t="inlineStr"/>
+      <c r="AL145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1</v>
+      </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20234,11 +20594,15 @@
       <c r="AK146" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL146" t="inlineStr"/>
-      <c r="AM146" t="inlineStr"/>
+      <c r="AL146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1</v>
+      </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20362,11 +20726,15 @@
       <c r="AK147" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL147" t="inlineStr"/>
-      <c r="AM147" t="inlineStr"/>
+      <c r="AL147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1</v>
+      </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20498,11 +20866,15 @@
       <c r="AK148" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL148" t="inlineStr"/>
-      <c r="AM148" t="inlineStr"/>
+      <c r="AL148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1</v>
+      </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20634,11 +21006,15 @@
       <c r="AK149" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL149" t="inlineStr"/>
-      <c r="AM149" t="inlineStr"/>
+      <c r="AL149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1</v>
+      </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20770,11 +21146,15 @@
       <c r="AK150" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL150" t="inlineStr"/>
-      <c r="AM150" t="inlineStr"/>
+      <c r="AL150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1</v>
+      </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20906,11 +21286,15 @@
       <c r="AK151" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL151" t="inlineStr"/>
-      <c r="AM151" t="inlineStr"/>
+      <c r="AL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1</v>
+      </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21042,11 +21426,15 @@
       <c r="AK152" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL152" t="inlineStr"/>
-      <c r="AM152" t="inlineStr"/>
+      <c r="AL152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1</v>
+      </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21178,11 +21566,15 @@
       <c r="AK153" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL153" t="inlineStr"/>
-      <c r="AM153" t="inlineStr"/>
+      <c r="AL153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1</v>
+      </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21314,11 +21706,15 @@
       <c r="AK154" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL154" t="inlineStr"/>
-      <c r="AM154" t="inlineStr"/>
+      <c r="AL154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1</v>
+      </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21450,11 +21846,15 @@
       <c r="AK155" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL155" t="inlineStr"/>
-      <c r="AM155" t="inlineStr"/>
+      <c r="AL155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1</v>
+      </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21586,11 +21986,15 @@
       <c r="AK156" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL156" t="inlineStr"/>
-      <c r="AM156" t="inlineStr"/>
+      <c r="AL156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>0</v>
+      </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21722,11 +22126,15 @@
       <c r="AK157" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL157" t="inlineStr"/>
-      <c r="AM157" t="inlineStr"/>
+      <c r="AL157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>0</v>
+      </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21858,11 +22266,15 @@
       <c r="AK158" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL158" t="inlineStr"/>
-      <c r="AM158" t="inlineStr"/>
+      <c r="AL158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>0</v>
+      </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21994,11 +22406,15 @@
       <c r="AK159" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL159" t="inlineStr"/>
-      <c r="AM159" t="inlineStr"/>
+      <c r="AL159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>0</v>
+      </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22130,11 +22546,15 @@
       <c r="AK160" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL160" t="inlineStr"/>
-      <c r="AM160" t="inlineStr"/>
+      <c r="AL160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>0</v>
+      </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22266,11 +22686,15 @@
       <c r="AK161" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL161" t="inlineStr"/>
-      <c r="AM161" t="inlineStr"/>
+      <c r="AL161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1</v>
+      </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22402,11 +22826,15 @@
       <c r="AK162" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL162" t="inlineStr"/>
-      <c r="AM162" t="inlineStr"/>
+      <c r="AL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1</v>
+      </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22538,11 +22966,15 @@
       <c r="AK163" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL163" t="inlineStr"/>
-      <c r="AM163" t="inlineStr"/>
+      <c r="AL163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1</v>
+      </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22674,11 +23106,15 @@
       <c r="AK164" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL164" t="inlineStr"/>
-      <c r="AM164" t="inlineStr"/>
+      <c r="AL164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1</v>
+      </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22810,11 +23246,15 @@
       <c r="AK165" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL165" t="inlineStr"/>
-      <c r="AM165" t="inlineStr"/>
+      <c r="AL165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1</v>
+      </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22946,11 +23386,15 @@
       <c r="AK166" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL166" t="inlineStr"/>
-      <c r="AM166" t="inlineStr"/>
+      <c r="AL166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>2</v>
+      </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23082,11 +23526,15 @@
       <c r="AK167" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL167" t="inlineStr"/>
-      <c r="AM167" t="inlineStr"/>
+      <c r="AL167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>2</v>
+      </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23218,11 +23666,15 @@
       <c r="AK168" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL168" t="inlineStr"/>
-      <c r="AM168" t="inlineStr"/>
+      <c r="AL168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>2</v>
+      </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23354,11 +23806,15 @@
       <c r="AK169" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL169" t="inlineStr"/>
-      <c r="AM169" t="inlineStr"/>
+      <c r="AL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>2</v>
+      </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23482,11 +23938,15 @@
       <c r="AK170" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL170" t="inlineStr"/>
-      <c r="AM170" t="inlineStr"/>
+      <c r="AL170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>2</v>
+      </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23610,11 +24070,15 @@
       <c r="AK171" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL171" t="inlineStr"/>
-      <c r="AM171" t="inlineStr"/>
+      <c r="AL171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>0</v>
+      </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23738,11 +24202,15 @@
       <c r="AK172" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL172" t="inlineStr"/>
-      <c r="AM172" t="inlineStr"/>
+      <c r="AL172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>0</v>
+      </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23874,11 +24342,15 @@
       <c r="AK173" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL173" t="inlineStr"/>
-      <c r="AM173" t="inlineStr"/>
+      <c r="AL173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>0</v>
+      </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24002,11 +24474,15 @@
       <c r="AK174" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL174" t="inlineStr"/>
-      <c r="AM174" t="inlineStr"/>
+      <c r="AL174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>0</v>
+      </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24130,11 +24606,15 @@
       <c r="AK175" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL175" t="inlineStr"/>
-      <c r="AM175" t="inlineStr"/>
+      <c r="AL175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>0</v>
+      </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24266,11 +24746,15 @@
       <c r="AK176" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL176" t="inlineStr"/>
-      <c r="AM176" t="inlineStr"/>
+      <c r="AL176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1</v>
+      </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24402,11 +24886,15 @@
       <c r="AK177" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL177" t="inlineStr"/>
-      <c r="AM177" t="inlineStr"/>
+      <c r="AL177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1</v>
+      </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24538,11 +25026,15 @@
       <c r="AK178" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL178" t="inlineStr"/>
-      <c r="AM178" t="inlineStr"/>
+      <c r="AL178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1</v>
+      </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24674,11 +25166,15 @@
       <c r="AK179" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL179" t="inlineStr"/>
-      <c r="AM179" t="inlineStr"/>
+      <c r="AL179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1</v>
+      </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24810,11 +25306,15 @@
       <c r="AK180" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL180" t="inlineStr"/>
-      <c r="AM180" t="inlineStr"/>
+      <c r="AL180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1</v>
+      </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24942,11 +25442,15 @@
       <c r="AK181" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL181" t="inlineStr"/>
-      <c r="AM181" t="inlineStr"/>
+      <c r="AL181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>0</v>
+      </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25054,11 +25558,15 @@
       <c r="AK182" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL182" t="inlineStr"/>
-      <c r="AM182" t="inlineStr"/>
+      <c r="AL182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>0</v>
+      </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25190,11 +25698,15 @@
       <c r="AK183" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL183" t="inlineStr"/>
-      <c r="AM183" t="inlineStr"/>
+      <c r="AL183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>0</v>
+      </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25318,11 +25830,15 @@
       <c r="AK184" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL184" t="inlineStr"/>
-      <c r="AM184" t="inlineStr"/>
+      <c r="AL184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>0</v>
+      </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25454,11 +25970,15 @@
       <c r="AK185" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL185" t="inlineStr"/>
-      <c r="AM185" t="inlineStr"/>
+      <c r="AL185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>0</v>
+      </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25586,11 +26106,15 @@
       <c r="AK186" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL186" t="inlineStr"/>
-      <c r="AM186" t="inlineStr"/>
+      <c r="AL186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1</v>
+      </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25722,11 +26246,15 @@
       <c r="AK187" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL187" t="inlineStr"/>
-      <c r="AM187" t="inlineStr"/>
+      <c r="AL187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1</v>
+      </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25858,11 +26386,15 @@
       <c r="AK188" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL188" t="inlineStr"/>
-      <c r="AM188" t="inlineStr"/>
+      <c r="AL188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1</v>
+      </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25994,11 +26526,15 @@
       <c r="AK189" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL189" t="inlineStr"/>
-      <c r="AM189" t="inlineStr"/>
+      <c r="AL189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1</v>
+      </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26122,11 +26658,15 @@
       <c r="AK190" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL190" t="inlineStr"/>
-      <c r="AM190" t="inlineStr"/>
+      <c r="AL190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1</v>
+      </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26258,11 +26798,15 @@
       <c r="AK191" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL191" t="inlineStr"/>
-      <c r="AM191" t="inlineStr"/>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1</v>
+      </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26386,11 +26930,15 @@
       <c r="AK192" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL192" t="inlineStr"/>
-      <c r="AM192" t="inlineStr"/>
+      <c r="AL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1</v>
+      </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26522,11 +27070,15 @@
       <c r="AK193" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL193" t="inlineStr"/>
-      <c r="AM193" t="inlineStr"/>
+      <c r="AL193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1</v>
+      </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26658,11 +27210,15 @@
       <c r="AK194" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL194" t="inlineStr"/>
-      <c r="AM194" t="inlineStr"/>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1</v>
+      </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26786,11 +27342,15 @@
       <c r="AK195" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL195" t="inlineStr"/>
-      <c r="AM195" t="inlineStr"/>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1</v>
+      </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26922,11 +27482,15 @@
       <c r="AK196" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL196" t="inlineStr"/>
-      <c r="AM196" t="inlineStr"/>
+      <c r="AL196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>0</v>
+      </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27034,11 +27598,15 @@
       <c r="AK197" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL197" t="inlineStr"/>
-      <c r="AM197" t="inlineStr"/>
+      <c r="AL197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>0</v>
+      </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27170,11 +27738,15 @@
       <c r="AK198" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL198" t="inlineStr"/>
-      <c r="AM198" t="inlineStr"/>
+      <c r="AL198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>0</v>
+      </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27306,11 +27878,15 @@
       <c r="AK199" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL199" t="inlineStr"/>
-      <c r="AM199" t="inlineStr"/>
+      <c r="AL199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>0</v>
+      </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27438,11 +28014,15 @@
       <c r="AK200" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL200" t="inlineStr"/>
-      <c r="AM200" t="inlineStr"/>
+      <c r="AL200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>0</v>
+      </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27570,11 +28150,15 @@
       <c r="AK201" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL201" t="inlineStr"/>
-      <c r="AM201" t="inlineStr"/>
+      <c r="AL201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1</v>
+      </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27706,11 +28290,15 @@
       <c r="AK202" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL202" t="inlineStr"/>
-      <c r="AM202" t="inlineStr"/>
+      <c r="AL202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1</v>
+      </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27842,11 +28430,15 @@
       <c r="AK203" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL203" t="inlineStr"/>
-      <c r="AM203" t="inlineStr"/>
+      <c r="AL203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1</v>
+      </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27978,11 +28570,15 @@
       <c r="AK204" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL204" t="inlineStr"/>
-      <c r="AM204" t="inlineStr"/>
+      <c r="AL204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1</v>
+      </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28114,11 +28710,15 @@
       <c r="AK205" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL205" t="inlineStr"/>
-      <c r="AM205" t="inlineStr"/>
+      <c r="AL205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1</v>
+      </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28250,11 +28850,15 @@
       <c r="AK206" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL206" t="inlineStr"/>
-      <c r="AM206" t="inlineStr"/>
+      <c r="AL206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>2</v>
+      </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28386,11 +28990,15 @@
       <c r="AK207" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL207" t="inlineStr"/>
-      <c r="AM207" t="inlineStr"/>
+      <c r="AL207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>2</v>
+      </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28522,11 +29130,15 @@
       <c r="AK208" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL208" t="inlineStr"/>
-      <c r="AM208" t="inlineStr"/>
+      <c r="AL208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>2</v>
+      </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28658,11 +29270,15 @@
       <c r="AK209" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL209" t="inlineStr"/>
-      <c r="AM209" t="inlineStr"/>
+      <c r="AL209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>2</v>
+      </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28794,11 +29410,15 @@
       <c r="AK210" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL210" t="inlineStr"/>
-      <c r="AM210" t="inlineStr"/>
+      <c r="AL210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>2</v>
+      </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28930,11 +29550,15 @@
       <c r="AK211" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL211" t="inlineStr"/>
-      <c r="AM211" t="inlineStr"/>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1</v>
+      </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29058,11 +29682,15 @@
       <c r="AK212" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL212" t="inlineStr"/>
-      <c r="AM212" t="inlineStr"/>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1</v>
+      </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29194,11 +29822,15 @@
       <c r="AK213" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL213" t="inlineStr"/>
-      <c r="AM213" t="inlineStr"/>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1</v>
+      </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29330,11 +29962,15 @@
       <c r="AK214" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL214" t="inlineStr"/>
-      <c r="AM214" t="inlineStr"/>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1</v>
+      </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29466,11 +30102,15 @@
       <c r="AK215" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL215" t="inlineStr"/>
-      <c r="AM215" t="inlineStr"/>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1</v>
+      </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29602,11 +30242,15 @@
       <c r="AK216" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL216" t="inlineStr"/>
-      <c r="AM216" t="inlineStr"/>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>0</v>
+      </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29714,11 +30358,15 @@
       <c r="AK217" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL217" t="inlineStr"/>
-      <c r="AM217" t="inlineStr"/>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>0</v>
+      </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29850,11 +30498,15 @@
       <c r="AK218" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL218" t="inlineStr"/>
-      <c r="AM218" t="inlineStr"/>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>0</v>
+      </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29978,11 +30630,15 @@
       <c r="AK219" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL219" t="inlineStr"/>
-      <c r="AM219" t="inlineStr"/>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>0</v>
+      </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30106,11 +30762,15 @@
       <c r="AK220" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL220" t="inlineStr"/>
-      <c r="AM220" t="inlineStr"/>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>0</v>
+      </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30242,11 +30902,15 @@
       <c r="AK221" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL221" t="inlineStr"/>
-      <c r="AM221" t="inlineStr"/>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>0</v>
+      </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30378,11 +31042,15 @@
       <c r="AK222" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL222" t="inlineStr"/>
-      <c r="AM222" t="inlineStr"/>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>0</v>
+      </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30514,11 +31182,15 @@
       <c r="AK223" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL223" t="inlineStr"/>
-      <c r="AM223" t="inlineStr"/>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>0</v>
+      </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30650,11 +31322,15 @@
       <c r="AK224" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL224" t="inlineStr"/>
-      <c r="AM224" t="inlineStr"/>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>0</v>
+      </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30786,11 +31462,15 @@
       <c r="AK225" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL225" t="inlineStr"/>
-      <c r="AM225" t="inlineStr"/>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>0</v>
+      </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30922,11 +31602,15 @@
       <c r="AK226" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL226" t="inlineStr"/>
-      <c r="AM226" t="inlineStr"/>
+      <c r="AL226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1</v>
+      </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31058,11 +31742,15 @@
       <c r="AK227" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL227" t="inlineStr"/>
-      <c r="AM227" t="inlineStr"/>
+      <c r="AL227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1</v>
+      </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31194,11 +31882,15 @@
       <c r="AK228" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL228" t="inlineStr"/>
-      <c r="AM228" t="inlineStr"/>
+      <c r="AL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1</v>
+      </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31330,11 +32022,15 @@
       <c r="AK229" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL229" t="inlineStr"/>
-      <c r="AM229" t="inlineStr"/>
+      <c r="AL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1</v>
+      </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31466,11 +32162,15 @@
       <c r="AK230" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL230" t="inlineStr"/>
-      <c r="AM230" t="inlineStr"/>
+      <c r="AL230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1</v>
+      </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16706,7 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19490,7 +19490,7 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19630,7 +19630,7 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20050,7 +20050,7 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20190,7 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -23946,7 +23946,7 @@
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24078,7 +24078,7 @@
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24350,7 +24350,7 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25034,7 +25034,7 @@
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25174,7 +25174,7 @@
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25314,7 +25314,7 @@
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25450,7 +25450,7 @@
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25706,7 +25706,7 @@
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25838,7 +25838,7 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25978,7 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26254,7 +26254,7 @@
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26394,7 +26394,7 @@
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26666,7 +26666,7 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26806,7 +26806,7 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -26938,7 +26938,7 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27490,7 +27490,7 @@
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27746,7 +27746,7 @@
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -27886,7 +27886,7 @@
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28158,7 +28158,7 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28578,7 +28578,7 @@
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28718,7 +28718,7 @@
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28858,7 +28858,7 @@
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -28998,7 +28998,7 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29278,7 +29278,7 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29418,7 +29418,7 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29690,7 +29690,7 @@
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29830,7 +29830,7 @@
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -29970,7 +29970,7 @@
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30250,7 +30250,7 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30506,7 +30506,7 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30638,7 +30638,7 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30770,7 +30770,7 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -30910,7 +30910,7 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31050,7 +31050,7 @@
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31470,7 +31470,7 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31610,7 +31610,7 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31750,7 +31750,7 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31890,7 +31890,7 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32030,7 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33150,7 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33570,7 +33570,7 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33850,7 @@
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34394,7 @@
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34666,7 +34666,7 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35358,7 +35358,7 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35630,7 +35630,7 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35770,7 +35770,7 @@
       </c>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35910,7 +35910,7 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36042,7 +36042,7 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36182,7 +36182,7 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36322,7 +36322,7 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37282,7 +37282,7 @@
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37554,7 +37554,7 @@
       </c>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37694,7 +37694,7 @@
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37834,7 +37834,7 @@
       </c>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AN273" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38254,7 @@
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38394,7 @@
       </c>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38534,7 +38534,7 @@
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38674,7 +38674,7 @@
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38814,7 +38814,7 @@
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38946,11 +38946,15 @@
       <c r="AK279" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL279" t="inlineStr"/>
-      <c r="AM279" t="inlineStr"/>
+      <c r="AL279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>1</v>
+      </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39082,11 +39086,15 @@
       <c r="AK280" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL280" t="inlineStr"/>
-      <c r="AM280" t="inlineStr"/>
+      <c r="AL280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>1</v>
+      </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39218,11 +39226,15 @@
       <c r="AK281" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL281" t="inlineStr"/>
-      <c r="AM281" t="inlineStr"/>
+      <c r="AL281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>1</v>
+      </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39354,11 +39366,15 @@
       <c r="AK282" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL282" t="inlineStr"/>
-      <c r="AM282" t="inlineStr"/>
+      <c r="AL282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>1</v>
+      </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39482,11 +39498,15 @@
       <c r="AK283" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL283" t="inlineStr"/>
-      <c r="AM283" t="inlineStr"/>
+      <c r="AL283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>1</v>
+      </c>
       <c r="AN283" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39618,11 +39638,15 @@
       <c r="AK284" t="n">
         <v>1.18</v>
       </c>
-      <c r="AL284" t="inlineStr"/>
-      <c r="AM284" t="inlineStr"/>
+      <c r="AL284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>1</v>
+      </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39754,11 +39778,15 @@
       <c r="AK285" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL285" t="inlineStr"/>
-      <c r="AM285" t="inlineStr"/>
+      <c r="AL285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>2</v>
+      </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39890,11 +39918,15 @@
       <c r="AK286" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL286" t="inlineStr"/>
-      <c r="AM286" t="inlineStr"/>
+      <c r="AL286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>2</v>
+      </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40026,11 +40058,15 @@
       <c r="AK287" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL287" t="inlineStr"/>
-      <c r="AM287" t="inlineStr"/>
+      <c r="AL287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>2</v>
+      </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40162,11 +40198,15 @@
       <c r="AK288" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL288" t="inlineStr"/>
-      <c r="AM288" t="inlineStr"/>
+      <c r="AL288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>2</v>
+      </c>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40298,11 +40338,15 @@
       <c r="AK289" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL289" t="inlineStr"/>
-      <c r="AM289" t="inlineStr"/>
+      <c r="AL289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>2</v>
+      </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40426,11 +40470,15 @@
       <c r="AK290" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL290" t="inlineStr"/>
-      <c r="AM290" t="inlineStr"/>
+      <c r="AL290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>2</v>
+      </c>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40554,11 +40602,15 @@
       <c r="AK291" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL291" t="inlineStr"/>
-      <c r="AM291" t="inlineStr"/>
+      <c r="AL291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>0</v>
+      </c>
       <c r="AN291" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40690,11 +40742,15 @@
       <c r="AK292" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL292" t="inlineStr"/>
-      <c r="AM292" t="inlineStr"/>
+      <c r="AL292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>0</v>
+      </c>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40818,11 +40874,15 @@
       <c r="AK293" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL293" t="inlineStr"/>
-      <c r="AM293" t="inlineStr"/>
+      <c r="AL293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>0</v>
+      </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40954,11 +41014,15 @@
       <c r="AK294" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL294" t="inlineStr"/>
-      <c r="AM294" t="inlineStr"/>
+      <c r="AL294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>0</v>
+      </c>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41090,11 +41154,15 @@
       <c r="AK295" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL295" t="inlineStr"/>
-      <c r="AM295" t="inlineStr"/>
+      <c r="AL295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>0</v>
+      </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41218,11 +41286,15 @@
       <c r="AK296" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL296" t="inlineStr"/>
-      <c r="AM296" t="inlineStr"/>
+      <c r="AL296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>0</v>
+      </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -48108,7 +48108,7 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B351" t="n">
         <v>390</v>
@@ -48136,10 +48136,14 @@
           <t>2025-10-11 16:00</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -48153,13 +48157,13 @@
         </is>
       </c>
       <c r="L351" t="n">
-        <v>0.3429659269431761</v>
+        <v>0.2011418822184691</v>
       </c>
       <c r="M351" t="n">
-        <v>0.3322993245014852</v>
+        <v>0.2907877178053431</v>
       </c>
       <c r="N351" t="n">
-        <v>0.3247347485553387</v>
+        <v>0.5080703999761879</v>
       </c>
       <c r="O351" t="n">
         <v>0.1020704514520514</v>
@@ -48240,7 +48244,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B352" t="n">
         <v>390</v>
@@ -48376,7 +48380,7 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B353" t="n">
         <v>390</v>
@@ -48512,7 +48516,7 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B354" t="n">
         <v>390</v>
@@ -48640,7 +48644,7 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B355" t="n">
         <v>390</v>
@@ -48776,7 +48780,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B356" t="n">
         <v>390</v>
@@ -48831,7 +48835,7 @@
         <v>0.3322993245014852</v>
       </c>
       <c r="N356" t="n">
-        <v>0.3247347485553387</v>
+        <v>0.3247347485553388</v>
       </c>
       <c r="O356" t="n">
         <v>0.1594213890890545</v>
@@ -48840,28 +48844,28 @@
         <v>0.8405786109109455</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.3438578129164602</v>
+        <v>0.3438578129164601</v>
       </c>
       <c r="R356" t="n">
-        <v>0.6561421870835398</v>
+        <v>0.6561421870835399</v>
       </c>
       <c r="S356" t="n">
-        <v>0.6069396571986343</v>
+        <v>0.6069396571986342</v>
       </c>
       <c r="T356" t="n">
-        <v>0.3930603428013657</v>
+        <v>0.3930603428013658</v>
       </c>
       <c r="U356" t="n">
         <v>0.7901421824726422</v>
       </c>
       <c r="V356" t="n">
-        <v>0.2098578175273577</v>
+        <v>0.2098578175273578</v>
       </c>
       <c r="W356" t="n">
-        <v>0.4526499008485075</v>
+        <v>0.4526499008485076</v>
       </c>
       <c r="X356" t="n">
-        <v>0.5473500991514925</v>
+        <v>0.5473500991514924</v>
       </c>
       <c r="Y356" t="n">
         <v>2.55</v>
@@ -48912,7 +48916,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B357" t="n">
         <v>325</v>
@@ -49048,7 +49052,7 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B358" t="n">
         <v>325</v>
@@ -49184,7 +49188,7 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B359" t="n">
         <v>325</v>
@@ -49320,7 +49324,7 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B360" t="n">
         <v>325</v>
@@ -49456,7 +49460,7 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B361" t="n">
         <v>325</v>
@@ -49584,7 +49588,7 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B362" t="n">
         <v>325</v>
@@ -49625,7 +49629,7 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="n">
-        <v>0.6506919052177617</v>
+        <v>0.6506919052177619</v>
       </c>
       <c r="M362" t="n">
         <v>0.2452004030999282</v>
@@ -49655,13 +49659,13 @@
         <v>0.607249393639822</v>
       </c>
       <c r="V362" t="n">
-        <v>0.392750606360178</v>
+        <v>0.3927506063601779</v>
       </c>
       <c r="W362" t="n">
-        <v>0.4158445681314062</v>
+        <v>0.4158445681314064</v>
       </c>
       <c r="X362" t="n">
-        <v>0.5841554318685938</v>
+        <v>0.5841554318685936</v>
       </c>
       <c r="Y362" t="n">
         <v>1.22</v>
@@ -49712,7 +49716,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B363" t="n">
         <v>390</v>
@@ -49740,10 +49744,14 @@
           <t>2025-10-12 16:00</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -49757,13 +49765,13 @@
         </is>
       </c>
       <c r="L363" t="n">
-        <v>0.5503132402106192</v>
+        <v>0.6085261239854647</v>
       </c>
       <c r="M363" t="n">
-        <v>0.2444196178791189</v>
+        <v>0.243796652524204</v>
       </c>
       <c r="N363" t="n">
-        <v>0.2052671419102617</v>
+        <v>0.1476772234903314</v>
       </c>
       <c r="O363" t="n">
         <v>0.09485128740002835</v>
@@ -49844,7 +49852,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B364" t="n">
         <v>390</v>
@@ -49980,7 +49988,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B365" t="n">
         <v>390</v>
@@ -50116,7 +50124,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B366" t="n">
         <v>390</v>
@@ -50252,7 +50260,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B367" t="n">
         <v>390</v>
@@ -50388,7 +50396,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B368" t="n">
         <v>390</v>
@@ -50440,16 +50448,16 @@
         <v>0.5503132402106192</v>
       </c>
       <c r="M368" t="n">
-        <v>0.2444196178791189</v>
+        <v>0.244419617879119</v>
       </c>
       <c r="N368" t="n">
         <v>0.2052671419102617</v>
       </c>
       <c r="O368" t="n">
-        <v>0.09386840194002266</v>
+        <v>0.09386840194002277</v>
       </c>
       <c r="P368" t="n">
-        <v>0.9061315980599773</v>
+        <v>0.9061315980599772</v>
       </c>
       <c r="Q368" t="n">
         <v>0.2907946001345738</v>
@@ -50458,16 +50466,16 @@
         <v>0.7092053998654262</v>
       </c>
       <c r="S368" t="n">
-        <v>0.5601939395715148</v>
+        <v>0.5601939395715149</v>
       </c>
       <c r="T368" t="n">
-        <v>0.4398060604284853</v>
+        <v>0.4398060604284851</v>
       </c>
       <c r="U368" t="n">
-        <v>0.8389483496533512</v>
+        <v>0.8389483496533513</v>
       </c>
       <c r="V368" t="n">
-        <v>0.1610516503466488</v>
+        <v>0.1610516503466487</v>
       </c>
       <c r="W368" t="n">
         <v>0.5500981273529454</v>
@@ -50524,7 +50532,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B369" t="n">
         <v>390</v>
@@ -50552,10 +50560,14 @@
           <t>2025-10-12 18:30</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -50569,13 +50581,13 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>0.5032479285748984</v>
+        <v>0.5640704465102414</v>
       </c>
       <c r="M369" t="n">
-        <v>0.313933159221518</v>
+        <v>0.2690406285215215</v>
       </c>
       <c r="N369" t="n">
-        <v>0.1828189122035837</v>
+        <v>0.166888924968237</v>
       </c>
       <c r="O369" t="n">
         <v>0.06102815402948403</v>
@@ -50656,7 +50668,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B370" t="n">
         <v>390</v>
@@ -50792,7 +50804,7 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B371" t="n">
         <v>390</v>
@@ -50928,7 +50940,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B372" t="n">
         <v>390</v>
@@ -51056,7 +51068,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B373" t="n">
         <v>390</v>
@@ -51184,7 +51196,7 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B374" t="n">
         <v>390</v>
@@ -51225,31 +51237,31 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="n">
-        <v>0.5032479285748984</v>
+        <v>0.5032479285748983</v>
       </c>
       <c r="M374" t="n">
-        <v>0.313933159221518</v>
+        <v>0.3139331592215179</v>
       </c>
       <c r="N374" t="n">
         <v>0.1828189122035837</v>
       </c>
       <c r="O374" t="n">
-        <v>0.03290281907865755</v>
+        <v>0.03290281907865744</v>
       </c>
       <c r="P374" t="n">
-        <v>0.9670971809213424</v>
+        <v>0.9670971809213426</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.368586231980446</v>
+        <v>0.3685862319804459</v>
       </c>
       <c r="R374" t="n">
-        <v>0.631413768019554</v>
+        <v>0.6314137680195541</v>
       </c>
       <c r="S374" t="n">
-        <v>0.5982532627776025</v>
+        <v>0.5982532627776024</v>
       </c>
       <c r="T374" t="n">
-        <v>0.4017467372223975</v>
+        <v>0.4017467372223976</v>
       </c>
       <c r="U374" t="n">
         <v>0.8273966579308216</v>
@@ -51258,10 +51270,10 @@
         <v>0.1726033420691783</v>
       </c>
       <c r="W374" t="n">
-        <v>0.5515892768954773</v>
+        <v>0.5515892768954772</v>
       </c>
       <c r="X374" t="n">
-        <v>0.4484107231045227</v>
+        <v>0.4484107231045228</v>
       </c>
       <c r="Y374" t="n">
         <v>1.91</v>
@@ -51312,7 +51324,7 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B375" t="n">
         <v>390</v>
@@ -51340,7 +51352,11 @@
           <t>2025-10-12 18:30</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I375" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -51357,13 +51373,13 @@
         </is>
       </c>
       <c r="L375" t="n">
-        <v>0.4297381803308904</v>
+        <v>0.4093210062914372</v>
       </c>
       <c r="M375" t="n">
-        <v>0.3372471649105066</v>
+        <v>0.3678741805175928</v>
       </c>
       <c r="N375" t="n">
-        <v>0.233014654758603</v>
+        <v>0.2228048131909701</v>
       </c>
       <c r="O375" t="n">
         <v>0.13885858945712</v>
@@ -51444,7 +51460,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B376" t="n">
         <v>390</v>
@@ -51580,7 +51596,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B377" t="n">
         <v>390</v>
@@ -51716,7 +51732,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B378" t="n">
         <v>390</v>
@@ -51852,7 +51868,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B379" t="n">
         <v>390</v>
@@ -51988,7 +52004,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B380" t="n">
         <v>390</v>
@@ -52037,19 +52053,19 @@
         </is>
       </c>
       <c r="L380" t="n">
-        <v>0.4297381803308904</v>
+        <v>0.4297381803308905</v>
       </c>
       <c r="M380" t="n">
-        <v>0.3372471649105066</v>
+        <v>0.3372471649105065</v>
       </c>
       <c r="N380" t="n">
         <v>0.233014654758603</v>
       </c>
       <c r="O380" t="n">
-        <v>0.06509688016033366</v>
+        <v>0.06509688016033399</v>
       </c>
       <c r="P380" t="n">
-        <v>0.9349031198396663</v>
+        <v>0.934903119839666</v>
       </c>
       <c r="Q380" t="n">
         <v>0.2903066358449774</v>
@@ -52058,16 +52074,16 @@
         <v>0.7096933641550226</v>
       </c>
       <c r="S380" t="n">
-        <v>0.64783451056643</v>
+        <v>0.6478345105664303</v>
       </c>
       <c r="T380" t="n">
-        <v>0.3521654894335699</v>
+        <v>0.3521654894335697</v>
       </c>
       <c r="U380" t="n">
         <v>0.7887373925621955</v>
       </c>
       <c r="V380" t="n">
-        <v>0.2112626074378045</v>
+        <v>0.2112626074378044</v>
       </c>
       <c r="W380" t="n">
         <v>0.4400353883571009</v>
@@ -52124,7 +52140,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B381" t="n">
         <v>390</v>
@@ -52152,7 +52168,11 @@
           <t>2025-10-12 20:30</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I381" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -52169,13 +52189,13 @@
         </is>
       </c>
       <c r="L381" t="n">
-        <v>0.4134723763376074</v>
+        <v>0.3783493792247689</v>
       </c>
       <c r="M381" t="n">
-        <v>0.2757685288000668</v>
+        <v>0.2850503593122609</v>
       </c>
       <c r="N381" t="n">
-        <v>0.3107590948623259</v>
+        <v>0.3366002614629702</v>
       </c>
       <c r="O381" t="n">
         <v>0.2527962945917361</v>
@@ -52256,7 +52276,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B382" t="n">
         <v>390</v>
@@ -52392,7 +52412,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B383" t="n">
         <v>390</v>
@@ -52520,7 +52540,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B384" t="n">
         <v>390</v>
@@ -52656,7 +52676,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B385" t="n">
         <v>390</v>
@@ -52792,7 +52812,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B386" t="n">
         <v>390</v>
@@ -52844,10 +52864,10 @@
         <v>0.4134723763376074</v>
       </c>
       <c r="M386" t="n">
-        <v>0.2757685288000668</v>
+        <v>0.2757685288000669</v>
       </c>
       <c r="N386" t="n">
-        <v>0.3107590948623259</v>
+        <v>0.3107590948623258</v>
       </c>
       <c r="O386" t="n">
         <v>0.07404933541947822</v>
@@ -52856,16 +52876,16 @@
         <v>0.9259506645805218</v>
       </c>
       <c r="Q386" t="n">
-        <v>0.38127902680665</v>
+        <v>0.3812790268066502</v>
       </c>
       <c r="R386" t="n">
-        <v>0.61872097319335</v>
+        <v>0.6187209731933498</v>
       </c>
       <c r="S386" t="n">
-        <v>0.7120694267462799</v>
+        <v>0.7120694267462797</v>
       </c>
       <c r="T386" t="n">
-        <v>0.2879305732537201</v>
+        <v>0.2879305732537203</v>
       </c>
       <c r="U386" t="n">
         <v>0.8868522984459558</v>
@@ -52874,10 +52894,10 @@
         <v>0.1131477015540442</v>
       </c>
       <c r="W386" t="n">
-        <v>0.444325399565536</v>
+        <v>0.4443253995655359</v>
       </c>
       <c r="X386" t="n">
-        <v>0.555674600434464</v>
+        <v>0.5556746004344641</v>
       </c>
       <c r="Y386" t="n">
         <v>2.3</v>
@@ -52928,7 +52948,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B387" t="n">
         <v>390</v>
@@ -52956,7 +52976,11 @@
           <t>2025-10-13 19:00</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
       <c r="I387" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -52973,13 +52997,13 @@
         </is>
       </c>
       <c r="L387" t="n">
-        <v>0.3815985662401618</v>
+        <v>0.2674762025986382</v>
       </c>
       <c r="M387" t="n">
-        <v>0.3334133461757773</v>
+        <v>0.3323066825251967</v>
       </c>
       <c r="N387" t="n">
-        <v>0.2849880875840612</v>
+        <v>0.4002171148761652</v>
       </c>
       <c r="O387" t="n">
         <v>0.143264303018712</v>
@@ -53060,7 +53084,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B388" t="n">
         <v>390</v>
@@ -53196,7 +53220,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B389" t="n">
         <v>390</v>
@@ -53332,7 +53356,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B390" t="n">
         <v>390</v>
@@ -53468,7 +53492,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B391" t="n">
         <v>390</v>
@@ -53604,7 +53628,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B392" t="n">
         <v>390</v>
@@ -53654,16 +53678,16 @@
         <v>0.2849880875840612</v>
       </c>
       <c r="O392" t="n">
-        <v>0.1444480827458108</v>
+        <v>0.1444480827458106</v>
       </c>
       <c r="P392" t="n">
-        <v>0.8555519172541892</v>
+        <v>0.8555519172541894</v>
       </c>
       <c r="Q392" t="n">
-        <v>0.398928412299504</v>
+        <v>0.3989284122995038</v>
       </c>
       <c r="R392" t="n">
-        <v>0.601071587700496</v>
+        <v>0.6010715877004962</v>
       </c>
       <c r="S392" t="n">
         <v>0.593455876156892</v>
@@ -53678,10 +53702,10 @@
         <v>0.1497494045938861</v>
       </c>
       <c r="W392" t="n">
-        <v>0.4373463133143936</v>
+        <v>0.4373463133143933</v>
       </c>
       <c r="X392" t="n">
-        <v>0.5626536866856064</v>
+        <v>0.5626536866856067</v>
       </c>
       <c r="Y392" t="n">
         <v>2.5</v>
@@ -53732,7 +53756,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B393" t="n">
         <v>390</v>
@@ -53760,10 +53784,14 @@
           <t>2025-10-13 21:30</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -53777,13 +53805,13 @@
         </is>
       </c>
       <c r="L393" t="n">
-        <v>0.5792133233484629</v>
+        <v>0.4656075114594619</v>
       </c>
       <c r="M393" t="n">
-        <v>0.2324624955755505</v>
+        <v>0.2838489780337718</v>
       </c>
       <c r="N393" t="n">
-        <v>0.1883241810759867</v>
+        <v>0.2505435105067663</v>
       </c>
       <c r="O393" t="n">
         <v>0.09159665960081764</v>
@@ -53864,7 +53892,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B394" t="n">
         <v>390</v>
@@ -54000,7 +54028,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B395" t="n">
         <v>390</v>
@@ -54136,7 +54164,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B396" t="n">
         <v>390</v>
@@ -54272,7 +54300,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B397" t="n">
         <v>390</v>
@@ -54408,7 +54436,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B398" t="n">
         <v>390</v>
@@ -54463,13 +54491,13 @@
         <v>0.2324624955755505</v>
       </c>
       <c r="N398" t="n">
-        <v>0.1883241810759867</v>
+        <v>0.1883241810759868</v>
       </c>
       <c r="O398" t="n">
-        <v>0.05445591112131898</v>
+        <v>0.05445591112131876</v>
       </c>
       <c r="P398" t="n">
-        <v>0.945544088878681</v>
+        <v>0.9455440888786812</v>
       </c>
       <c r="Q398" t="n">
         <v>0.3258649482344571</v>
@@ -54490,10 +54518,10 @@
         <v>0.2331971554824679</v>
       </c>
       <c r="W398" t="n">
-        <v>0.4920442711405159</v>
+        <v>0.4920442711405158</v>
       </c>
       <c r="X398" t="n">
-        <v>0.507955728859484</v>
+        <v>0.5079557288594843</v>
       </c>
       <c r="Y398" t="n">
         <v>1.57</v>
@@ -54544,7 +54572,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B399" t="n">
         <v>390</v>
@@ -54572,10 +54600,14 @@
           <t>2025-10-14 19:30</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -54589,13 +54621,13 @@
         </is>
       </c>
       <c r="L399" t="n">
-        <v>0.6353262209473194</v>
+        <v>0.4754403614542098</v>
       </c>
       <c r="M399" t="n">
-        <v>0.1711855435829157</v>
+        <v>0.1433167424138836</v>
       </c>
       <c r="N399" t="n">
-        <v>0.1934882354697649</v>
+        <v>0.3812428961319068</v>
       </c>
       <c r="O399" t="n">
         <v>0.05373764801376313</v>
@@ -54676,7 +54708,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B400" t="n">
         <v>390</v>
@@ -54812,7 +54844,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B401" t="n">
         <v>390</v>
@@ -54948,7 +54980,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B402" t="n">
         <v>390</v>
@@ -55084,7 +55116,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B403" t="n">
         <v>390</v>
@@ -55220,7 +55252,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B404" t="n">
         <v>390</v>
@@ -55269,7 +55301,7 @@
         </is>
       </c>
       <c r="L404" t="n">
-        <v>0.6353262209473194</v>
+        <v>0.6353262209473198</v>
       </c>
       <c r="M404" t="n">
         <v>0.1711855435829157</v>
@@ -55284,10 +55316,10 @@
         <v>0.968509173335794</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.2652485056649185</v>
+        <v>0.2652485056649188</v>
       </c>
       <c r="R404" t="n">
-        <v>0.7347514943350815</v>
+        <v>0.7347514943350812</v>
       </c>
       <c r="S404" t="n">
         <v>0.4982202925848063</v>
@@ -55296,16 +55328,16 @@
         <v>0.5017797074151937</v>
       </c>
       <c r="U404" t="n">
-        <v>0.7086189245957711</v>
+        <v>0.7086189245957712</v>
       </c>
       <c r="V404" t="n">
-        <v>0.2913810754042289</v>
+        <v>0.2913810754042288</v>
       </c>
       <c r="W404" t="n">
-        <v>0.5470911664608166</v>
+        <v>0.5470911664608165</v>
       </c>
       <c r="X404" t="n">
-        <v>0.4529088335391834</v>
+        <v>0.4529088335391835</v>
       </c>
       <c r="Y404" t="n">
         <v>1.61</v>
@@ -55356,7 +55388,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B405" t="n">
         <v>390</v>
@@ -55384,10 +55416,14 @@
           <t>2025-10-14 19:30</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -55401,13 +55437,13 @@
         </is>
       </c>
       <c r="L405" t="n">
-        <v>0.3678274953893951</v>
+        <v>0.2243854660371182</v>
       </c>
       <c r="M405" t="n">
-        <v>0.2761646625437316</v>
+        <v>0.1729616485866504</v>
       </c>
       <c r="N405" t="n">
-        <v>0.3560078420668735</v>
+        <v>0.6026528853762314</v>
       </c>
       <c r="O405" t="n">
         <v>0.09564563809742621</v>
@@ -55488,7 +55524,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B406" t="n">
         <v>390</v>
@@ -55624,7 +55660,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B407" t="n">
         <v>390</v>
@@ -55760,7 +55796,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B408" t="n">
         <v>390</v>
@@ -55896,7 +55932,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B409" t="n">
         <v>390</v>
@@ -56032,7 +56068,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B410" t="n">
         <v>390</v>
@@ -56073,19 +56109,19 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="n">
-        <v>0.3678274953893951</v>
+        <v>0.3678274953893952</v>
       </c>
       <c r="M410" t="n">
         <v>0.2761646625437316</v>
       </c>
       <c r="N410" t="n">
-        <v>0.3560078420668735</v>
+        <v>0.3560078420668732</v>
       </c>
       <c r="O410" t="n">
-        <v>0.1306546269481101</v>
+        <v>0.1306546269481099</v>
       </c>
       <c r="P410" t="n">
-        <v>0.8693453730518899</v>
+        <v>0.8693453730518901</v>
       </c>
       <c r="Q410" t="n">
         <v>0.3877514148942766</v>
@@ -56094,19 +56130,19 @@
         <v>0.6122485851057234</v>
       </c>
       <c r="S410" t="n">
-        <v>0.6274450384917454</v>
+        <v>0.6274450384917455</v>
       </c>
       <c r="T410" t="n">
-        <v>0.3725549615082546</v>
+        <v>0.3725549615082545</v>
       </c>
       <c r="U410" t="n">
         <v>0.8337786548610733</v>
       </c>
       <c r="V410" t="n">
-        <v>0.1662213451389268</v>
+        <v>0.1662213451389267</v>
       </c>
       <c r="W410" t="n">
-        <v>0.4427436752676188</v>
+        <v>0.4427436752676189</v>
       </c>
       <c r="X410" t="n">
         <v>0.5572563247323812</v>
@@ -56160,7 +56196,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B411" t="n">
         <v>390</v>
@@ -56188,7 +56224,11 @@
           <t>2025-10-14 21:30</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="I411" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56205,13 +56245,13 @@
         </is>
       </c>
       <c r="L411" t="n">
-        <v>0.6290405024071873</v>
+        <v>0.441358442087512</v>
       </c>
       <c r="M411" t="n">
-        <v>0.1816944810979464</v>
+        <v>0.2636707203278639</v>
       </c>
       <c r="N411" t="n">
-        <v>0.1892650164948664</v>
+        <v>0.2949708375846241</v>
       </c>
       <c r="O411" t="n">
         <v>0.07656947436946315</v>
@@ -56292,7 +56332,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B412" t="n">
         <v>390</v>
@@ -56428,7 +56468,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B413" t="n">
         <v>390</v>
@@ -56564,7 +56604,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B414" t="n">
         <v>390</v>
@@ -56700,7 +56740,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B415" t="n">
         <v>390</v>
@@ -56836,7 +56876,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>45940.49006944444</v>
+        <v>45940.49365740741</v>
       </c>
       <c r="B416" t="n">
         <v>390</v>
@@ -56885,7 +56925,7 @@
         </is>
       </c>
       <c r="L416" t="n">
-        <v>0.6290405024071873</v>
+        <v>0.6290405024071876</v>
       </c>
       <c r="M416" t="n">
         <v>0.1816944810979464</v>
@@ -56894,34 +56934,34 @@
         <v>0.1892650164948664</v>
       </c>
       <c r="O416" t="n">
-        <v>0.03122995870045764</v>
+        <v>0.03122995870045731</v>
       </c>
       <c r="P416" t="n">
-        <v>0.9687700412995424</v>
+        <v>0.9687700412995427</v>
       </c>
       <c r="Q416" t="n">
-        <v>0.3242852105707751</v>
+        <v>0.3242852105707752</v>
       </c>
       <c r="R416" t="n">
-        <v>0.6757147894292249</v>
+        <v>0.6757147894292248</v>
       </c>
       <c r="S416" t="n">
-        <v>0.6268205566972485</v>
+        <v>0.6268205566972486</v>
       </c>
       <c r="T416" t="n">
-        <v>0.3731794433027515</v>
+        <v>0.3731794433027514</v>
       </c>
       <c r="U416" t="n">
         <v>0.8472269609792713</v>
       </c>
       <c r="V416" t="n">
-        <v>0.1527730390207288</v>
+        <v>0.1527730390207287</v>
       </c>
       <c r="W416" t="n">
-        <v>0.5225373595199284</v>
+        <v>0.5225373595199285</v>
       </c>
       <c r="X416" t="n">
-        <v>0.4774626404800716</v>
+        <v>0.4774626404800715</v>
       </c>
       <c r="Y416" t="n">
         <v>1.51</v>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -2434,11 +2434,15 @@
       <c r="AK14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2</v>
+      </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2570,11 +2574,15 @@
       <c r="AK15" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2</v>
+      </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2706,11 +2714,15 @@
       <c r="AK16" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2</v>
+      </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2842,11 +2854,15 @@
       <c r="AK17" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2</v>
+      </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2978,11 +2994,15 @@
       <c r="AK18" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2</v>
+      </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3114,11 +3134,15 @@
       <c r="AK19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2</v>
+      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3250,11 +3274,15 @@
       <c r="AK20" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2</v>
+      </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3386,11 +3414,15 @@
       <c r="AK21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2</v>
+      </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3514,11 +3546,15 @@
       <c r="AK22" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2</v>
+      </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3642,11 +3678,15 @@
       <c r="AK23" t="n">
         <v>1.3</v>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>2</v>
+      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3778,11 +3818,15 @@
       <c r="AK24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>3</v>
+      </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -3910,11 +3954,15 @@
       <c r="AK25" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>3</v>
+      </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4046,11 +4094,15 @@
       <c r="AK26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>3</v>
+      </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4182,11 +4234,15 @@
       <c r="AK27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>3</v>
+      </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4318,11 +4374,15 @@
       <c r="AK28" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>3</v>
+      </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4454,11 +4514,15 @@
       <c r="AK29" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4590,11 +4654,15 @@
       <c r="AK30" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4718,11 +4786,15 @@
       <c r="AK31" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4854,11 +4926,15 @@
       <c r="AK32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -4982,11 +5058,15 @@
       <c r="AK33" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5118,11 +5198,15 @@
       <c r="AK34" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5230,11 +5314,15 @@
       <c r="AK35" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5366,11 +5454,15 @@
       <c r="AK36" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5502,11 +5594,15 @@
       <c r="AK37" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5638,11 +5734,15 @@
       <c r="AK38" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5770,11 +5870,15 @@
       <c r="AK39" t="n">
         <v>2</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -5882,11 +5986,15 @@
       <c r="AK40" t="n">
         <v>2</v>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1</v>
+      </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6018,11 +6126,15 @@
       <c r="AK41" t="n">
         <v>2</v>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1</v>
+      </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6154,11 +6266,15 @@
       <c r="AK42" t="n">
         <v>2</v>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1</v>
+      </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6282,11 +6398,15 @@
       <c r="AK43" t="n">
         <v>2</v>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1</v>
+      </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6418,11 +6538,15 @@
       <c r="AK44" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1</v>
+      </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6530,11 +6654,15 @@
       <c r="AK45" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AL45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1</v>
+      </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6666,11 +6794,15 @@
       <c r="AK46" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6802,11 +6934,15 @@
       <c r="AK47" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -6930,11 +7066,15 @@
       <c r="AK48" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
+      <c r="AL48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7066,11 +7206,15 @@
       <c r="AK49" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
+      <c r="AL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7178,11 +7322,15 @@
       <c r="AK50" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
+      <c r="AL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7306,11 +7454,15 @@
       <c r="AK51" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
+      <c r="AL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7434,11 +7586,15 @@
       <c r="AK52" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
+      <c r="AL52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7570,11 +7726,15 @@
       <c r="AK53" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
+      <c r="AL53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7698,11 +7858,15 @@
       <c r="AK54" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7834,11 +7998,15 @@
       <c r="AK55" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -7970,11 +8138,15 @@
       <c r="AK56" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
+      <c r="AL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8106,11 +8278,15 @@
       <c r="AK57" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8234,11 +8410,15 @@
       <c r="AK58" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8370,11 +8550,15 @@
       <c r="AK59" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8506,11 +8690,15 @@
       <c r="AK60" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
+      <c r="AL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8642,11 +8830,15 @@
       <c r="AK61" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8778,11 +8970,15 @@
       <c r="AK62" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -8910,11 +9106,15 @@
       <c r="AK63" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9046,11 +9246,15 @@
       <c r="AK64" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1</v>
+      </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9182,11 +9386,15 @@
       <c r="AK65" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1</v>
+      </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9318,11 +9526,15 @@
       <c r="AK66" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1</v>
+      </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9454,11 +9666,15 @@
       <c r="AK67" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1</v>
+      </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9590,11 +9806,15 @@
       <c r="AK68" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1</v>
+      </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9726,11 +9946,15 @@
       <c r="AK69" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
+      <c r="AL69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1</v>
+      </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9862,11 +10086,15 @@
       <c r="AK70" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
+      <c r="AL70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1</v>
+      </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -9998,11 +10226,15 @@
       <c r="AK71" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
+      <c r="AL71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1</v>
+      </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10134,11 +10366,15 @@
       <c r="AK72" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
+      <c r="AL72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1</v>
+      </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10262,11 +10498,15 @@
       <c r="AK73" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
+      <c r="AL73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1</v>
+      </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10390,11 +10630,15 @@
       <c r="AK74" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1</v>
+      </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10526,11 +10770,15 @@
       <c r="AK75" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1</v>
+      </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10658,11 +10906,15 @@
       <c r="AK76" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1</v>
+      </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10794,11 +11046,15 @@
       <c r="AK77" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
+      <c r="AL77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1</v>
+      </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -10930,11 +11186,15 @@
       <c r="AK78" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
+      <c r="AL78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1</v>
+      </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11066,11 +11326,15 @@
       <c r="AK79" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
+      <c r="AL79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1</v>
+      </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11202,11 +11466,15 @@
       <c r="AK80" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
+      <c r="AL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1</v>
+      </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11330,11 +11598,15 @@
       <c r="AK81" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
+      <c r="AL81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1</v>
+      </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11466,11 +11738,15 @@
       <c r="AK82" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr"/>
+      <c r="AL82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1</v>
+      </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11602,11 +11878,15 @@
       <c r="AK83" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1</v>
+      </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11734,11 +12014,15 @@
       <c r="AK84" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr"/>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>3</v>
+      </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11846,11 +12130,15 @@
       <c r="AK85" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="inlineStr"/>
+      <c r="AL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>3</v>
+      </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -11974,11 +12262,15 @@
       <c r="AK86" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="inlineStr"/>
+      <c r="AL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>3</v>
+      </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12106,11 +12398,15 @@
       <c r="AK87" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr"/>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>3</v>
+      </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12238,11 +12534,15 @@
       <c r="AK88" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="inlineStr"/>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>3</v>
+      </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12366,11 +12666,15 @@
       <c r="AK89" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
+      <c r="AL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1</v>
+      </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12502,11 +12806,15 @@
       <c r="AK90" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="inlineStr"/>
+      <c r="AL90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1</v>
+      </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12638,11 +12946,15 @@
       <c r="AK91" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="inlineStr"/>
+      <c r="AL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1</v>
+      </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12774,11 +13086,15 @@
       <c r="AK92" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="inlineStr"/>
+      <c r="AL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1</v>
+      </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -12910,11 +13226,15 @@
       <c r="AK93" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr"/>
+      <c r="AL93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1</v>
+      </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13374,7 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13514,7 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13654,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13794,7 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13934,7 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13754,7 +14074,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -13878,11 +14198,15 @@
       <c r="AK100" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="inlineStr"/>
+      <c r="AL100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1</v>
+      </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14014,11 +14338,15 @@
       <c r="AK101" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="inlineStr"/>
+      <c r="AL101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1</v>
+      </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14150,11 +14478,15 @@
       <c r="AK102" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="inlineStr"/>
+      <c r="AL102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1</v>
+      </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14286,11 +14618,15 @@
       <c r="AK103" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
+      <c r="AL103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1</v>
+      </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14418,11 +14754,15 @@
       <c r="AK104" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="inlineStr"/>
+      <c r="AL104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1</v>
+      </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14902,7 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14694,7 +15034,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14834,7 +15174,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -14974,7 +15314,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15454,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15594,7 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15734,7 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15874,7 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15674,7 +16014,7 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15814,7 +16154,7 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -15954,7 +16294,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16426,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16566,7 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16706,7 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16846,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16646,7 +16986,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16786,7 +17126,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -16926,7 +17266,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17406,7 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17546,7 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17686,7 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17826,7 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17626,7 +17966,7 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17766,7 +18106,7 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -17898,7 +18238,7 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18378,7 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18170,7 +18510,7 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18650,7 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18790,7 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18930,7 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18730,7 +19070,7 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -18870,7 +19210,7 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19010,7 +19350,7 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19150,7 +19490,7 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19290,7 +19630,7 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19770,7 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -19562,11 +19902,15 @@
       <c r="AK141" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL141" t="inlineStr"/>
-      <c r="AM141" t="inlineStr"/>
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1</v>
+      </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19698,11 +20042,15 @@
       <c r="AK142" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL142" t="inlineStr"/>
-      <c r="AM142" t="inlineStr"/>
+      <c r="AL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1</v>
+      </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19834,11 +20182,15 @@
       <c r="AK143" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL143" t="inlineStr"/>
-      <c r="AM143" t="inlineStr"/>
+      <c r="AL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1</v>
+      </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19970,11 +20322,15 @@
       <c r="AK144" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL144" t="inlineStr"/>
-      <c r="AM144" t="inlineStr"/>
+      <c r="AL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1</v>
+      </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20106,11 +20462,15 @@
       <c r="AK145" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL145" t="inlineStr"/>
-      <c r="AM145" t="inlineStr"/>
+      <c r="AL145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1</v>
+      </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20234,11 +20594,15 @@
       <c r="AK146" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL146" t="inlineStr"/>
-      <c r="AM146" t="inlineStr"/>
+      <c r="AL146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1</v>
+      </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20362,11 +20726,15 @@
       <c r="AK147" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL147" t="inlineStr"/>
-      <c r="AM147" t="inlineStr"/>
+      <c r="AL147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1</v>
+      </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20498,11 +20866,15 @@
       <c r="AK148" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL148" t="inlineStr"/>
-      <c r="AM148" t="inlineStr"/>
+      <c r="AL148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1</v>
+      </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20634,11 +21006,15 @@
       <c r="AK149" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL149" t="inlineStr"/>
-      <c r="AM149" t="inlineStr"/>
+      <c r="AL149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1</v>
+      </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20770,11 +21146,15 @@
       <c r="AK150" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL150" t="inlineStr"/>
-      <c r="AM150" t="inlineStr"/>
+      <c r="AL150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1</v>
+      </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -20906,11 +21286,15 @@
       <c r="AK151" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL151" t="inlineStr"/>
-      <c r="AM151" t="inlineStr"/>
+      <c r="AL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1</v>
+      </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21042,11 +21426,15 @@
       <c r="AK152" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL152" t="inlineStr"/>
-      <c r="AM152" t="inlineStr"/>
+      <c r="AL152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1</v>
+      </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21178,11 +21566,15 @@
       <c r="AK153" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL153" t="inlineStr"/>
-      <c r="AM153" t="inlineStr"/>
+      <c r="AL153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1</v>
+      </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21314,11 +21706,15 @@
       <c r="AK154" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL154" t="inlineStr"/>
-      <c r="AM154" t="inlineStr"/>
+      <c r="AL154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1</v>
+      </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21450,11 +21846,15 @@
       <c r="AK155" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL155" t="inlineStr"/>
-      <c r="AM155" t="inlineStr"/>
+      <c r="AL155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1</v>
+      </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21586,11 +21986,15 @@
       <c r="AK156" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL156" t="inlineStr"/>
-      <c r="AM156" t="inlineStr"/>
+      <c r="AL156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>0</v>
+      </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21722,11 +22126,15 @@
       <c r="AK157" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL157" t="inlineStr"/>
-      <c r="AM157" t="inlineStr"/>
+      <c r="AL157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>0</v>
+      </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21858,11 +22266,15 @@
       <c r="AK158" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL158" t="inlineStr"/>
-      <c r="AM158" t="inlineStr"/>
+      <c r="AL158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>0</v>
+      </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -21994,11 +22406,15 @@
       <c r="AK159" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL159" t="inlineStr"/>
-      <c r="AM159" t="inlineStr"/>
+      <c r="AL159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>0</v>
+      </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22130,11 +22546,15 @@
       <c r="AK160" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL160" t="inlineStr"/>
-      <c r="AM160" t="inlineStr"/>
+      <c r="AL160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>0</v>
+      </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22266,11 +22686,15 @@
       <c r="AK161" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL161" t="inlineStr"/>
-      <c r="AM161" t="inlineStr"/>
+      <c r="AL161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1</v>
+      </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22402,11 +22826,15 @@
       <c r="AK162" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL162" t="inlineStr"/>
-      <c r="AM162" t="inlineStr"/>
+      <c r="AL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1</v>
+      </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22538,11 +22966,15 @@
       <c r="AK163" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL163" t="inlineStr"/>
-      <c r="AM163" t="inlineStr"/>
+      <c r="AL163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1</v>
+      </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22674,11 +23106,15 @@
       <c r="AK164" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL164" t="inlineStr"/>
-      <c r="AM164" t="inlineStr"/>
+      <c r="AL164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1</v>
+      </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22810,11 +23246,15 @@
       <c r="AK165" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL165" t="inlineStr"/>
-      <c r="AM165" t="inlineStr"/>
+      <c r="AL165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1</v>
+      </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -22946,11 +23386,15 @@
       <c r="AK166" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL166" t="inlineStr"/>
-      <c r="AM166" t="inlineStr"/>
+      <c r="AL166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>2</v>
+      </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23082,11 +23526,15 @@
       <c r="AK167" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL167" t="inlineStr"/>
-      <c r="AM167" t="inlineStr"/>
+      <c r="AL167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>2</v>
+      </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23218,11 +23666,15 @@
       <c r="AK168" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL168" t="inlineStr"/>
-      <c r="AM168" t="inlineStr"/>
+      <c r="AL168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>2</v>
+      </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23354,11 +23806,15 @@
       <c r="AK169" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL169" t="inlineStr"/>
-      <c r="AM169" t="inlineStr"/>
+      <c r="AL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>2</v>
+      </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23482,11 +23938,15 @@
       <c r="AK170" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL170" t="inlineStr"/>
-      <c r="AM170" t="inlineStr"/>
+      <c r="AL170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>2</v>
+      </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23610,11 +24070,15 @@
       <c r="AK171" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL171" t="inlineStr"/>
-      <c r="AM171" t="inlineStr"/>
+      <c r="AL171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>0</v>
+      </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23738,11 +24202,15 @@
       <c r="AK172" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL172" t="inlineStr"/>
-      <c r="AM172" t="inlineStr"/>
+      <c r="AL172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>0</v>
+      </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -23874,11 +24342,15 @@
       <c r="AK173" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL173" t="inlineStr"/>
-      <c r="AM173" t="inlineStr"/>
+      <c r="AL173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>0</v>
+      </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24002,11 +24474,15 @@
       <c r="AK174" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL174" t="inlineStr"/>
-      <c r="AM174" t="inlineStr"/>
+      <c r="AL174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>0</v>
+      </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24130,11 +24606,15 @@
       <c r="AK175" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL175" t="inlineStr"/>
-      <c r="AM175" t="inlineStr"/>
+      <c r="AL175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>0</v>
+      </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24266,11 +24746,15 @@
       <c r="AK176" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL176" t="inlineStr"/>
-      <c r="AM176" t="inlineStr"/>
+      <c r="AL176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1</v>
+      </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24402,11 +24886,15 @@
       <c r="AK177" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL177" t="inlineStr"/>
-      <c r="AM177" t="inlineStr"/>
+      <c r="AL177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1</v>
+      </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24538,11 +25026,15 @@
       <c r="AK178" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL178" t="inlineStr"/>
-      <c r="AM178" t="inlineStr"/>
+      <c r="AL178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1</v>
+      </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24674,11 +25166,15 @@
       <c r="AK179" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL179" t="inlineStr"/>
-      <c r="AM179" t="inlineStr"/>
+      <c r="AL179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1</v>
+      </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24810,11 +25306,15 @@
       <c r="AK180" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL180" t="inlineStr"/>
-      <c r="AM180" t="inlineStr"/>
+      <c r="AL180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1</v>
+      </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -24942,11 +25442,15 @@
       <c r="AK181" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL181" t="inlineStr"/>
-      <c r="AM181" t="inlineStr"/>
+      <c r="AL181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>0</v>
+      </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25054,11 +25558,15 @@
       <c r="AK182" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL182" t="inlineStr"/>
-      <c r="AM182" t="inlineStr"/>
+      <c r="AL182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>0</v>
+      </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25190,11 +25698,15 @@
       <c r="AK183" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL183" t="inlineStr"/>
-      <c r="AM183" t="inlineStr"/>
+      <c r="AL183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>0</v>
+      </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25318,11 +25830,15 @@
       <c r="AK184" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL184" t="inlineStr"/>
-      <c r="AM184" t="inlineStr"/>
+      <c r="AL184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>0</v>
+      </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25454,11 +25970,15 @@
       <c r="AK185" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL185" t="inlineStr"/>
-      <c r="AM185" t="inlineStr"/>
+      <c r="AL185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>0</v>
+      </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25586,11 +26106,15 @@
       <c r="AK186" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL186" t="inlineStr"/>
-      <c r="AM186" t="inlineStr"/>
+      <c r="AL186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1</v>
+      </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25722,11 +26246,15 @@
       <c r="AK187" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL187" t="inlineStr"/>
-      <c r="AM187" t="inlineStr"/>
+      <c r="AL187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1</v>
+      </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25858,11 +26386,15 @@
       <c r="AK188" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL188" t="inlineStr"/>
-      <c r="AM188" t="inlineStr"/>
+      <c r="AL188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1</v>
+      </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -25994,11 +26526,15 @@
       <c r="AK189" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL189" t="inlineStr"/>
-      <c r="AM189" t="inlineStr"/>
+      <c r="AL189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1</v>
+      </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26122,11 +26658,15 @@
       <c r="AK190" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL190" t="inlineStr"/>
-      <c r="AM190" t="inlineStr"/>
+      <c r="AL190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1</v>
+      </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26258,11 +26798,15 @@
       <c r="AK191" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL191" t="inlineStr"/>
-      <c r="AM191" t="inlineStr"/>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1</v>
+      </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26386,11 +26930,15 @@
       <c r="AK192" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL192" t="inlineStr"/>
-      <c r="AM192" t="inlineStr"/>
+      <c r="AL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1</v>
+      </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26522,11 +27070,15 @@
       <c r="AK193" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL193" t="inlineStr"/>
-      <c r="AM193" t="inlineStr"/>
+      <c r="AL193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1</v>
+      </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26658,11 +27210,15 @@
       <c r="AK194" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL194" t="inlineStr"/>
-      <c r="AM194" t="inlineStr"/>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1</v>
+      </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26786,11 +27342,15 @@
       <c r="AK195" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL195" t="inlineStr"/>
-      <c r="AM195" t="inlineStr"/>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1</v>
+      </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -26922,11 +27482,15 @@
       <c r="AK196" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL196" t="inlineStr"/>
-      <c r="AM196" t="inlineStr"/>
+      <c r="AL196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>0</v>
+      </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27034,11 +27598,15 @@
       <c r="AK197" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL197" t="inlineStr"/>
-      <c r="AM197" t="inlineStr"/>
+      <c r="AL197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>0</v>
+      </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27170,11 +27738,15 @@
       <c r="AK198" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL198" t="inlineStr"/>
-      <c r="AM198" t="inlineStr"/>
+      <c r="AL198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>0</v>
+      </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27306,11 +27878,15 @@
       <c r="AK199" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL199" t="inlineStr"/>
-      <c r="AM199" t="inlineStr"/>
+      <c r="AL199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>0</v>
+      </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27438,11 +28014,15 @@
       <c r="AK200" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL200" t="inlineStr"/>
-      <c r="AM200" t="inlineStr"/>
+      <c r="AL200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>0</v>
+      </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27570,11 +28150,15 @@
       <c r="AK201" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL201" t="inlineStr"/>
-      <c r="AM201" t="inlineStr"/>
+      <c r="AL201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1</v>
+      </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27706,11 +28290,15 @@
       <c r="AK202" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL202" t="inlineStr"/>
-      <c r="AM202" t="inlineStr"/>
+      <c r="AL202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1</v>
+      </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27842,11 +28430,15 @@
       <c r="AK203" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL203" t="inlineStr"/>
-      <c r="AM203" t="inlineStr"/>
+      <c r="AL203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1</v>
+      </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -27978,11 +28570,15 @@
       <c r="AK204" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL204" t="inlineStr"/>
-      <c r="AM204" t="inlineStr"/>
+      <c r="AL204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1</v>
+      </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28114,11 +28710,15 @@
       <c r="AK205" t="n">
         <v>1.22</v>
       </c>
-      <c r="AL205" t="inlineStr"/>
-      <c r="AM205" t="inlineStr"/>
+      <c r="AL205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1</v>
+      </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28250,11 +28850,15 @@
       <c r="AK206" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL206" t="inlineStr"/>
-      <c r="AM206" t="inlineStr"/>
+      <c r="AL206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>2</v>
+      </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28386,11 +28990,15 @@
       <c r="AK207" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL207" t="inlineStr"/>
-      <c r="AM207" t="inlineStr"/>
+      <c r="AL207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>2</v>
+      </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28522,11 +29130,15 @@
       <c r="AK208" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL208" t="inlineStr"/>
-      <c r="AM208" t="inlineStr"/>
+      <c r="AL208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>2</v>
+      </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28658,11 +29270,15 @@
       <c r="AK209" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL209" t="inlineStr"/>
-      <c r="AM209" t="inlineStr"/>
+      <c r="AL209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>2</v>
+      </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28794,11 +29410,15 @@
       <c r="AK210" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL210" t="inlineStr"/>
-      <c r="AM210" t="inlineStr"/>
+      <c r="AL210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>2</v>
+      </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -28930,11 +29550,15 @@
       <c r="AK211" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL211" t="inlineStr"/>
-      <c r="AM211" t="inlineStr"/>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1</v>
+      </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29058,11 +29682,15 @@
       <c r="AK212" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL212" t="inlineStr"/>
-      <c r="AM212" t="inlineStr"/>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1</v>
+      </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29194,11 +29822,15 @@
       <c r="AK213" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL213" t="inlineStr"/>
-      <c r="AM213" t="inlineStr"/>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1</v>
+      </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29330,11 +29962,15 @@
       <c r="AK214" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL214" t="inlineStr"/>
-      <c r="AM214" t="inlineStr"/>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1</v>
+      </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29466,11 +30102,15 @@
       <c r="AK215" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL215" t="inlineStr"/>
-      <c r="AM215" t="inlineStr"/>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1</v>
+      </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29602,11 +30242,15 @@
       <c r="AK216" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL216" t="inlineStr"/>
-      <c r="AM216" t="inlineStr"/>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>0</v>
+      </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29714,11 +30358,15 @@
       <c r="AK217" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL217" t="inlineStr"/>
-      <c r="AM217" t="inlineStr"/>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>0</v>
+      </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29850,11 +30498,15 @@
       <c r="AK218" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL218" t="inlineStr"/>
-      <c r="AM218" t="inlineStr"/>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>0</v>
+      </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -29978,11 +30630,15 @@
       <c r="AK219" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL219" t="inlineStr"/>
-      <c r="AM219" t="inlineStr"/>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>0</v>
+      </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30106,11 +30762,15 @@
       <c r="AK220" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL220" t="inlineStr"/>
-      <c r="AM220" t="inlineStr"/>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>0</v>
+      </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30242,11 +30902,15 @@
       <c r="AK221" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL221" t="inlineStr"/>
-      <c r="AM221" t="inlineStr"/>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>0</v>
+      </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30378,11 +31042,15 @@
       <c r="AK222" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL222" t="inlineStr"/>
-      <c r="AM222" t="inlineStr"/>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>0</v>
+      </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30514,11 +31182,15 @@
       <c r="AK223" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL223" t="inlineStr"/>
-      <c r="AM223" t="inlineStr"/>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>0</v>
+      </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30650,11 +31322,15 @@
       <c r="AK224" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL224" t="inlineStr"/>
-      <c r="AM224" t="inlineStr"/>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>0</v>
+      </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30786,11 +31462,15 @@
       <c r="AK225" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL225" t="inlineStr"/>
-      <c r="AM225" t="inlineStr"/>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>0</v>
+      </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -30922,11 +31602,15 @@
       <c r="AK226" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL226" t="inlineStr"/>
-      <c r="AM226" t="inlineStr"/>
+      <c r="AL226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1</v>
+      </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31058,11 +31742,15 @@
       <c r="AK227" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL227" t="inlineStr"/>
-      <c r="AM227" t="inlineStr"/>
+      <c r="AL227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1</v>
+      </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31194,11 +31882,15 @@
       <c r="AK228" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL228" t="inlineStr"/>
-      <c r="AM228" t="inlineStr"/>
+      <c r="AL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1</v>
+      </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31330,11 +32022,15 @@
       <c r="AK229" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL229" t="inlineStr"/>
-      <c r="AM229" t="inlineStr"/>
+      <c r="AL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1</v>
+      </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31466,11 +32162,15 @@
       <c r="AK230" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL230" t="inlineStr"/>
-      <c r="AM230" t="inlineStr"/>
+      <c r="AL230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1</v>
+      </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -31610,7 +32310,7 @@
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31750,7 +32450,7 @@
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -31890,7 +32590,7 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32730,7 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32170,7 +32870,7 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32310,7 +33010,7 @@
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32450,7 +33150,7 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32590,7 +33290,7 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32730,7 +33430,7 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -32870,7 +33570,7 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33010,7 +33710,7 @@
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33850,7 @@
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33990,7 @@
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33422,7 +34122,7 @@
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33562,7 +34262,7 @@
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33694,7 +34394,7 @@
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33826,7 +34526,7 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -33966,7 +34666,7 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34106,7 +34806,7 @@
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34238,7 +34938,7 @@
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34378,7 +35078,7 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34518,7 +35218,7 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34658,7 +35358,7 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34790,7 +35490,7 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -34930,7 +35630,7 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35070,7 +35770,7 @@
       </c>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35210,7 +35910,7 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35342,7 +36042,7 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35482,7 +36182,7 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35622,7 +36322,7 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35762,7 +36462,7 @@
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -35894,7 +36594,7 @@
       </c>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36034,7 +36734,7 @@
       </c>
       <c r="AN263" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36170,7 +36870,7 @@
       </c>
       <c r="AN264" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36310,7 +37010,7 @@
       </c>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36450,7 +37150,7 @@
       </c>
       <c r="AN266" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36582,7 +37282,7 @@
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36722,7 +37422,7 @@
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36854,7 +37554,7 @@
       </c>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -36994,7 +37694,7 @@
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37134,7 +37834,7 @@
       </c>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37274,7 +37974,7 @@
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37414,7 +38114,7 @@
       </c>
       <c r="AN273" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37554,7 +38254,7 @@
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37694,7 +38394,7 @@
       </c>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37834,7 +38534,7 @@
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -37974,7 +38674,7 @@
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38814,7 @@
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38954,7 @@
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38394,7 +39094,7 @@
       </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38534,7 +39234,7 @@
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38674,7 +39374,7 @@
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38806,7 +39506,7 @@
       </c>
       <c r="AN283" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -38946,7 +39646,7 @@
       </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39086,7 +39786,7 @@
       </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39226,7 +39926,7 @@
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39366,7 +40066,7 @@
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39506,7 +40206,7 @@
       </c>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39646,7 +40346,7 @@
       </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39778,7 +40478,7 @@
       </c>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -39910,7 +40610,7 @@
       </c>
       <c r="AN291" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40050,7 +40750,7 @@
       </c>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40182,7 +40882,7 @@
       </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40322,7 +41022,7 @@
       </c>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40462,7 +41162,7 @@
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40594,7 +41294,7 @@
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40734,7 +41434,7 @@
       </c>
       <c r="AN297" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -40874,7 +41574,7 @@
       </c>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41014,7 +41714,7 @@
       </c>
       <c r="AN299" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41150,7 +41850,7 @@
       </c>
       <c r="AN300" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41290,7 +41990,7 @@
       </c>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41430,7 +42130,7 @@
       </c>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41570,7 +42270,7 @@
       </c>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41710,7 +42410,7 @@
       </c>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41850,7 +42550,7 @@
       </c>
       <c r="AN305" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -41990,7 +42690,7 @@
       </c>
       <c r="AN306" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42122,7 +42822,7 @@
       </c>
       <c r="AN307" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42262,7 +42962,7 @@
       </c>
       <c r="AN308" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42402,7 +43102,7 @@
       </c>
       <c r="AN309" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42542,7 +43242,7 @@
       </c>
       <c r="AN310" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42682,7 +43382,7 @@
       </c>
       <c r="AN311" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42822,7 +43522,7 @@
       </c>
       <c r="AN312" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -42962,7 +43662,7 @@
       </c>
       <c r="AN313" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43094,7 +43794,7 @@
       </c>
       <c r="AN314" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43234,7 +43934,7 @@
       </c>
       <c r="AN315" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43374,7 +44074,7 @@
       </c>
       <c r="AN316" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43514,7 +44214,7 @@
       </c>
       <c r="AN317" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43654,7 +44354,7 @@
       </c>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43794,7 +44494,7 @@
       </c>
       <c r="AN319" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -43926,7 +44626,7 @@
       </c>
       <c r="AN320" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44066,7 +44766,7 @@
       </c>
       <c r="AN321" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44206,7 +44906,7 @@
       </c>
       <c r="AN322" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44346,7 +45046,7 @@
       </c>
       <c r="AN323" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44482,7 +45182,7 @@
       </c>
       <c r="AN324" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44622,7 +45322,7 @@
       </c>
       <c r="AN325" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44762,7 +45462,7 @@
       </c>
       <c r="AN326" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -44902,7 +45602,7 @@
       </c>
       <c r="AN327" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45042,7 +45742,7 @@
       </c>
       <c r="AN328" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45182,7 +45882,7 @@
       </c>
       <c r="AN329" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45322,7 +46022,7 @@
       </c>
       <c r="AN330" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45462,7 +46162,7 @@
       </c>
       <c r="AN331" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45602,7 +46302,7 @@
       </c>
       <c r="AN332" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45734,7 +46434,7 @@
       </c>
       <c r="AN333" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -45874,7 +46574,7 @@
       </c>
       <c r="AN334" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46006,7 +46706,7 @@
       </c>
       <c r="AN335" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46146,7 +46846,7 @@
       </c>
       <c r="AN336" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46286,7 +46986,7 @@
       </c>
       <c r="AN337" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46426,7 +47126,7 @@
       </c>
       <c r="AN338" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46566,7 +47266,7 @@
       </c>
       <c r="AN339" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46706,7 +47406,7 @@
       </c>
       <c r="AN340" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46846,7 +47546,7 @@
       </c>
       <c r="AN341" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -46986,7 +47686,7 @@
       </c>
       <c r="AN342" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47826,7 @@
       </c>
       <c r="AN343" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47266,7 +47966,7 @@
       </c>
       <c r="AN344" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47406,7 +48106,7 @@
       </c>
       <c r="AN345" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47546,7 +48246,7 @@
       </c>
       <c r="AN346" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47686,7 +48386,7 @@
       </c>
       <c r="AN347" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47822,7 +48522,7 @@
       </c>
       <c r="AN348" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -47962,7 +48662,7 @@
       </c>
       <c r="AN349" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>
@@ -48102,7 +48802,7 @@
       </c>
       <c r="AN350" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>nostarted</t>
         </is>
       </c>
     </row>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16706,7 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17546,7 +17546,7 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17826,7 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19490,7 +19490,7 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19630,7 +19630,7 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -32590,7 +32590,7 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -32730,7 +32730,7 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33010,7 +33010,7 @@
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33150,7 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33570,7 +33570,7 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33850,7 @@
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34394,7 @@
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34666,7 +34666,7 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35358,7 +35358,7 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35630,7 +35630,7 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35770,7 +35770,7 @@
       </c>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -35910,7 +35910,7 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36042,7 +36042,7 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36182,7 +36182,7 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36322,7 +36322,7 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36594,7 +36594,7 @@
       </c>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36734,7 +36734,7 @@
       </c>
       <c r="AN263" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -36870,7 +36870,7 @@
       </c>
       <c r="AN264" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37010,7 +37010,7 @@
       </c>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37150,7 +37150,7 @@
       </c>
       <c r="AN266" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37282,7 +37282,7 @@
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37554,7 +37554,7 @@
       </c>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37694,7 +37694,7 @@
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37834,7 +37834,7 @@
       </c>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AN273" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38254,7 @@
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38394,7 @@
       </c>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38534,7 +38534,7 @@
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38674,7 +38674,7 @@
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38814,7 +38814,7 @@
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -38954,7 +38954,7 @@
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39094,7 +39094,7 @@
       </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39234,7 +39234,7 @@
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39374,7 +39374,7 @@
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39506,7 +39506,7 @@
       </c>
       <c r="AN283" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39646,7 +39646,7 @@
       </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39786,7 +39786,7 @@
       </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -39926,7 +39926,7 @@
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40066,7 +40066,7 @@
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40206,7 +40206,7 @@
       </c>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40346,7 +40346,7 @@
       </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40610,7 +40610,7 @@
       </c>
       <c r="AN291" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40750,7 +40750,7 @@
       </c>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -40882,7 +40882,7 @@
       </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41022,7 +41022,7 @@
       </c>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41162,7 +41162,7 @@
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41294,7 +41294,7 @@
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41434,7 +41434,7 @@
       </c>
       <c r="AN297" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41714,7 +41714,7 @@
       </c>
       <c r="AN299" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41850,7 +41850,7 @@
       </c>
       <c r="AN300" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42130,7 +42130,7 @@
       </c>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42410,7 +42410,7 @@
       </c>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42550,7 +42550,7 @@
       </c>
       <c r="AN305" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42690,7 +42690,7 @@
       </c>
       <c r="AN306" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AN307" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -42962,7 +42962,7 @@
       </c>
       <c r="AN308" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43102,7 +43102,7 @@
       </c>
       <c r="AN309" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43242,7 +43242,7 @@
       </c>
       <c r="AN310" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43382,7 +43382,7 @@
       </c>
       <c r="AN311" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43522,7 +43522,7 @@
       </c>
       <c r="AN312" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43662,7 +43662,7 @@
       </c>
       <c r="AN313" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="AN314" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AN315" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44074,7 +44074,7 @@
       </c>
       <c r="AN316" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44214,7 +44214,7 @@
       </c>
       <c r="AN317" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44354,7 +44354,7 @@
       </c>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44494,7 +44494,7 @@
       </c>
       <c r="AN319" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44626,7 +44626,7 @@
       </c>
       <c r="AN320" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="AN321" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -44906,7 +44906,7 @@
       </c>
       <c r="AN322" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45046,7 +45046,7 @@
       </c>
       <c r="AN323" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45182,7 +45182,7 @@
       </c>
       <c r="AN324" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="AN325" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45462,7 +45462,7 @@
       </c>
       <c r="AN326" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45602,7 +45602,7 @@
       </c>
       <c r="AN327" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="AN328" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -45882,7 +45882,7 @@
       </c>
       <c r="AN329" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46022,7 +46022,7 @@
       </c>
       <c r="AN330" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46162,7 +46162,7 @@
       </c>
       <c r="AN331" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46302,7 +46302,7 @@
       </c>
       <c r="AN332" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46434,7 +46434,7 @@
       </c>
       <c r="AN333" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46574,7 +46574,7 @@
       </c>
       <c r="AN334" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46706,7 +46706,7 @@
       </c>
       <c r="AN335" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46846,7 +46846,7 @@
       </c>
       <c r="AN336" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -46986,7 +46986,7 @@
       </c>
       <c r="AN337" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="AN338" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47266,7 +47266,7 @@
       </c>
       <c r="AN339" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47406,7 +47406,7 @@
       </c>
       <c r="AN340" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47546,7 +47546,7 @@
       </c>
       <c r="AN341" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47686,7 +47686,7 @@
       </c>
       <c r="AN342" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47826,7 +47826,7 @@
       </c>
       <c r="AN343" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -47966,7 +47966,7 @@
       </c>
       <c r="AN344" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="AN345" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48246,7 +48246,7 @@
       </c>
       <c r="AN346" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48386,7 +48386,7 @@
       </c>
       <c r="AN347" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48522,7 +48522,7 @@
       </c>
       <c r="AN348" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48662,7 +48662,7 @@
       </c>
       <c r="AN349" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
@@ -48802,13 +48802,13 @@
       </c>
       <c r="AN350" t="inlineStr">
         <is>
-          <t>nostarted</t>
+          <t>finished</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B351" t="n">
         <v>390</v>
@@ -48838,12 +48838,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Visitante</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -48857,13 +48857,13 @@
         </is>
       </c>
       <c r="L351" t="n">
-        <v>0.2011418822184691</v>
+        <v>0.3429659269431761</v>
       </c>
       <c r="M351" t="n">
-        <v>0.2907877178053431</v>
+        <v>0.3322993245014851</v>
       </c>
       <c r="N351" t="n">
-        <v>0.5080703999761879</v>
+        <v>0.3247347485553387</v>
       </c>
       <c r="O351" t="n">
         <v>0.1020704514520514</v>
@@ -48944,7 +48944,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B352" t="n">
         <v>390</v>
@@ -49080,7 +49080,7 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B353" t="n">
         <v>390</v>
@@ -49216,7 +49216,7 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B354" t="n">
         <v>390</v>
@@ -49344,7 +49344,7 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B355" t="n">
         <v>390</v>
@@ -49480,7 +49480,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B356" t="n">
         <v>390</v>
@@ -49532,10 +49532,10 @@
         <v>0.3429659269431761</v>
       </c>
       <c r="M356" t="n">
-        <v>0.3322993245014852</v>
+        <v>0.3322993245014851</v>
       </c>
       <c r="N356" t="n">
-        <v>0.3247347485553388</v>
+        <v>0.3247347485553387</v>
       </c>
       <c r="O356" t="n">
         <v>0.1594213890890545</v>
@@ -49544,22 +49544,22 @@
         <v>0.8405786109109455</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.3438578129164601</v>
+        <v>0.3438578129164603</v>
       </c>
       <c r="R356" t="n">
-        <v>0.6561421870835399</v>
+        <v>0.6561421870835397</v>
       </c>
       <c r="S356" t="n">
-        <v>0.6069396571986342</v>
+        <v>0.6069396571986343</v>
       </c>
       <c r="T356" t="n">
-        <v>0.3930603428013658</v>
+        <v>0.3930603428013657</v>
       </c>
       <c r="U356" t="n">
         <v>0.7901421824726422</v>
       </c>
       <c r="V356" t="n">
-        <v>0.2098578175273578</v>
+        <v>0.2098578175273577</v>
       </c>
       <c r="W356" t="n">
         <v>0.4526499008485076</v>
@@ -50416,7 +50416,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B363" t="n">
         <v>390</v>
@@ -50451,7 +50451,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -50465,13 +50465,13 @@
         </is>
       </c>
       <c r="L363" t="n">
-        <v>0.6085261239854647</v>
+        <v>0.5503132402106193</v>
       </c>
       <c r="M363" t="n">
-        <v>0.243796652524204</v>
+        <v>0.2444196178791189</v>
       </c>
       <c r="N363" t="n">
-        <v>0.1476772234903314</v>
+        <v>0.2052671419102617</v>
       </c>
       <c r="O363" t="n">
         <v>0.09485128740002835</v>
@@ -50552,7 +50552,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B364" t="n">
         <v>390</v>
@@ -50688,7 +50688,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B365" t="n">
         <v>390</v>
@@ -50824,7 +50824,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B366" t="n">
         <v>390</v>
@@ -50960,7 +50960,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B367" t="n">
         <v>390</v>
@@ -51096,7 +51096,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B368" t="n">
         <v>390</v>
@@ -51145,19 +51145,19 @@
         </is>
       </c>
       <c r="L368" t="n">
-        <v>0.5503132402106192</v>
+        <v>0.5503132402106193</v>
       </c>
       <c r="M368" t="n">
-        <v>0.244419617879119</v>
+        <v>0.2444196178791189</v>
       </c>
       <c r="N368" t="n">
         <v>0.2052671419102617</v>
       </c>
       <c r="O368" t="n">
-        <v>0.09386840194002277</v>
+        <v>0.09386840194002288</v>
       </c>
       <c r="P368" t="n">
-        <v>0.9061315980599772</v>
+        <v>0.9061315980599771</v>
       </c>
       <c r="Q368" t="n">
         <v>0.2907946001345738</v>
@@ -51166,10 +51166,10 @@
         <v>0.7092053998654262</v>
       </c>
       <c r="S368" t="n">
-        <v>0.5601939395715149</v>
+        <v>0.5601939395715148</v>
       </c>
       <c r="T368" t="n">
-        <v>0.4398060604284851</v>
+        <v>0.4398060604284852</v>
       </c>
       <c r="U368" t="n">
         <v>0.8389483496533513</v>
@@ -51178,10 +51178,10 @@
         <v>0.1610516503466487</v>
       </c>
       <c r="W368" t="n">
-        <v>0.5500981273529454</v>
+        <v>0.5500981273529453</v>
       </c>
       <c r="X368" t="n">
-        <v>0.4499018726470546</v>
+        <v>0.4499018726470547</v>
       </c>
       <c r="Y368" t="n">
         <v>1.86</v>
@@ -51232,7 +51232,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B369" t="n">
         <v>390</v>
@@ -51267,7 +51267,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -51281,13 +51281,13 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>0.5640704465102414</v>
+        <v>0.5032479285748984</v>
       </c>
       <c r="M369" t="n">
-        <v>0.2690406285215215</v>
+        <v>0.313933159221518</v>
       </c>
       <c r="N369" t="n">
-        <v>0.166888924968237</v>
+        <v>0.1828189122035836</v>
       </c>
       <c r="O369" t="n">
         <v>0.06102815402948403</v>
@@ -51368,7 +51368,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B370" t="n">
         <v>390</v>
@@ -51504,7 +51504,7 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B371" t="n">
         <v>390</v>
@@ -51640,7 +51640,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B372" t="n">
         <v>390</v>
@@ -51768,7 +51768,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B373" t="n">
         <v>390</v>
@@ -51896,7 +51896,7 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B374" t="n">
         <v>390</v>
@@ -51937,25 +51937,25 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="n">
-        <v>0.5032479285748983</v>
+        <v>0.5032479285748984</v>
       </c>
       <c r="M374" t="n">
-        <v>0.3139331592215179</v>
+        <v>0.313933159221518</v>
       </c>
       <c r="N374" t="n">
-        <v>0.1828189122035837</v>
+        <v>0.1828189122035836</v>
       </c>
       <c r="O374" t="n">
-        <v>0.03290281907865744</v>
+        <v>0.03290281907865722</v>
       </c>
       <c r="P374" t="n">
-        <v>0.9670971809213426</v>
+        <v>0.9670971809213428</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.3685862319804459</v>
+        <v>0.368586231980446</v>
       </c>
       <c r="R374" t="n">
-        <v>0.6314137680195541</v>
+        <v>0.631413768019554</v>
       </c>
       <c r="S374" t="n">
         <v>0.5982532627776024</v>
@@ -51967,13 +51967,13 @@
         <v>0.8273966579308216</v>
       </c>
       <c r="V374" t="n">
-        <v>0.1726033420691783</v>
+        <v>0.1726033420691784</v>
       </c>
       <c r="W374" t="n">
-        <v>0.5515892768954772</v>
+        <v>0.5515892768954774</v>
       </c>
       <c r="X374" t="n">
-        <v>0.4484107231045228</v>
+        <v>0.4484107231045226</v>
       </c>
       <c r="Y374" t="n">
         <v>1.91</v>
@@ -52024,7 +52024,7 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B375" t="n">
         <v>390</v>
@@ -52073,13 +52073,13 @@
         </is>
       </c>
       <c r="L375" t="n">
-        <v>0.4093210062914372</v>
+        <v>0.4297381803308904</v>
       </c>
       <c r="M375" t="n">
-        <v>0.3678741805175928</v>
+        <v>0.3372471649105065</v>
       </c>
       <c r="N375" t="n">
-        <v>0.2228048131909701</v>
+        <v>0.2330146547586029</v>
       </c>
       <c r="O375" t="n">
         <v>0.13885858945712</v>
@@ -52160,7 +52160,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B376" t="n">
         <v>390</v>
@@ -52296,7 +52296,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B377" t="n">
         <v>390</v>
@@ -52432,7 +52432,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B378" t="n">
         <v>390</v>
@@ -52568,7 +52568,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B379" t="n">
         <v>390</v>
@@ -52704,7 +52704,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B380" t="n">
         <v>390</v>
@@ -52753,13 +52753,13 @@
         </is>
       </c>
       <c r="L380" t="n">
-        <v>0.4297381803308905</v>
+        <v>0.4297381803308904</v>
       </c>
       <c r="M380" t="n">
         <v>0.3372471649105065</v>
       </c>
       <c r="N380" t="n">
-        <v>0.233014654758603</v>
+        <v>0.2330146547586029</v>
       </c>
       <c r="O380" t="n">
         <v>0.06509688016033399</v>
@@ -52768,16 +52768,16 @@
         <v>0.934903119839666</v>
       </c>
       <c r="Q380" t="n">
-        <v>0.2903066358449774</v>
+        <v>0.2903066358449776</v>
       </c>
       <c r="R380" t="n">
-        <v>0.7096933641550226</v>
+        <v>0.7096933641550224</v>
       </c>
       <c r="S380" t="n">
-        <v>0.6478345105664303</v>
+        <v>0.64783451056643</v>
       </c>
       <c r="T380" t="n">
-        <v>0.3521654894335697</v>
+        <v>0.3521654894335699</v>
       </c>
       <c r="U380" t="n">
         <v>0.7887373925621955</v>
@@ -52840,7 +52840,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B381" t="n">
         <v>390</v>
@@ -52889,13 +52889,13 @@
         </is>
       </c>
       <c r="L381" t="n">
-        <v>0.3783493792247689</v>
+        <v>0.4134723763376076</v>
       </c>
       <c r="M381" t="n">
-        <v>0.2850503593122609</v>
+        <v>0.2757685288000669</v>
       </c>
       <c r="N381" t="n">
-        <v>0.3366002614629702</v>
+        <v>0.3107590948623259</v>
       </c>
       <c r="O381" t="n">
         <v>0.2527962945917361</v>
@@ -52976,7 +52976,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B382" t="n">
         <v>390</v>
@@ -53112,7 +53112,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B383" t="n">
         <v>390</v>
@@ -53240,7 +53240,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B384" t="n">
         <v>390</v>
@@ -53376,7 +53376,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B385" t="n">
         <v>390</v>
@@ -53512,7 +53512,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B386" t="n">
         <v>390</v>
@@ -53561,31 +53561,31 @@
         </is>
       </c>
       <c r="L386" t="n">
-        <v>0.4134723763376074</v>
+        <v>0.4134723763376076</v>
       </c>
       <c r="M386" t="n">
         <v>0.2757685288000669</v>
       </c>
       <c r="N386" t="n">
-        <v>0.3107590948623258</v>
+        <v>0.3107590948623259</v>
       </c>
       <c r="O386" t="n">
-        <v>0.07404933541947822</v>
+        <v>0.07404933541947833</v>
       </c>
       <c r="P386" t="n">
-        <v>0.9259506645805218</v>
+        <v>0.9259506645805217</v>
       </c>
       <c r="Q386" t="n">
-        <v>0.3812790268066502</v>
+        <v>0.3812790268066503</v>
       </c>
       <c r="R386" t="n">
-        <v>0.6187209731933498</v>
+        <v>0.6187209731933497</v>
       </c>
       <c r="S386" t="n">
         <v>0.7120694267462797</v>
       </c>
       <c r="T386" t="n">
-        <v>0.2879305732537203</v>
+        <v>0.2879305732537202</v>
       </c>
       <c r="U386" t="n">
         <v>0.8868522984459558</v>
@@ -53648,7 +53648,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B387" t="n">
         <v>390</v>
@@ -53678,7 +53678,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Visitante</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53697,13 +53697,13 @@
         </is>
       </c>
       <c r="L387" t="n">
-        <v>0.2674762025986382</v>
+        <v>0.3815985662401618</v>
       </c>
       <c r="M387" t="n">
-        <v>0.3323066825251967</v>
+        <v>0.3334133461757773</v>
       </c>
       <c r="N387" t="n">
-        <v>0.4002171148761652</v>
+        <v>0.2849880875840611</v>
       </c>
       <c r="O387" t="n">
         <v>0.143264303018712</v>
@@ -53784,7 +53784,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B388" t="n">
         <v>390</v>
@@ -53920,7 +53920,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B389" t="n">
         <v>390</v>
@@ -54056,7 +54056,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B390" t="n">
         <v>390</v>
@@ -54192,7 +54192,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B391" t="n">
         <v>390</v>
@@ -54328,7 +54328,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B392" t="n">
         <v>390</v>
@@ -54375,25 +54375,25 @@
         <v>0.3334133461757773</v>
       </c>
       <c r="N392" t="n">
-        <v>0.2849880875840612</v>
+        <v>0.2849880875840611</v>
       </c>
       <c r="O392" t="n">
-        <v>0.1444480827458106</v>
+        <v>0.1444480827458107</v>
       </c>
       <c r="P392" t="n">
-        <v>0.8555519172541894</v>
+        <v>0.8555519172541893</v>
       </c>
       <c r="Q392" t="n">
-        <v>0.3989284122995038</v>
+        <v>0.3989284122995039</v>
       </c>
       <c r="R392" t="n">
-        <v>0.6010715877004962</v>
+        <v>0.6010715877004961</v>
       </c>
       <c r="S392" t="n">
         <v>0.593455876156892</v>
       </c>
       <c r="T392" t="n">
-        <v>0.4065441238431081</v>
+        <v>0.406544123843108</v>
       </c>
       <c r="U392" t="n">
         <v>0.8502505954061139</v>
@@ -54402,7 +54402,7 @@
         <v>0.1497494045938861</v>
       </c>
       <c r="W392" t="n">
-        <v>0.4373463133143933</v>
+        <v>0.4373463133143934</v>
       </c>
       <c r="X392" t="n">
         <v>0.5626536866856067</v>
@@ -54456,7 +54456,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B393" t="n">
         <v>390</v>
@@ -54491,7 +54491,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -54505,13 +54505,13 @@
         </is>
       </c>
       <c r="L393" t="n">
-        <v>0.4656075114594619</v>
+        <v>0.5792133233484628</v>
       </c>
       <c r="M393" t="n">
-        <v>0.2838489780337718</v>
+        <v>0.2324624955755505</v>
       </c>
       <c r="N393" t="n">
-        <v>0.2505435105067663</v>
+        <v>0.1883241810759868</v>
       </c>
       <c r="O393" t="n">
         <v>0.09159665960081764</v>
@@ -54592,7 +54592,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B394" t="n">
         <v>390</v>
@@ -54728,7 +54728,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B395" t="n">
         <v>390</v>
@@ -54864,7 +54864,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B396" t="n">
         <v>390</v>
@@ -55000,7 +55000,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B397" t="n">
         <v>390</v>
@@ -55136,7 +55136,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B398" t="n">
         <v>390</v>
@@ -55185,7 +55185,7 @@
         </is>
       </c>
       <c r="L398" t="n">
-        <v>0.5792133233484629</v>
+        <v>0.5792133233484628</v>
       </c>
       <c r="M398" t="n">
         <v>0.2324624955755505</v>
@@ -55194,16 +55194,16 @@
         <v>0.1883241810759868</v>
       </c>
       <c r="O398" t="n">
-        <v>0.05445591112131876</v>
+        <v>0.05445591112131887</v>
       </c>
       <c r="P398" t="n">
-        <v>0.9455440888786812</v>
+        <v>0.9455440888786811</v>
       </c>
       <c r="Q398" t="n">
-        <v>0.3258649482344571</v>
+        <v>0.325864948234457</v>
       </c>
       <c r="R398" t="n">
-        <v>0.6741350517655429</v>
+        <v>0.674135051765543</v>
       </c>
       <c r="S398" t="n">
         <v>0.4946378891932037</v>
@@ -55218,10 +55218,10 @@
         <v>0.2331971554824679</v>
       </c>
       <c r="W398" t="n">
-        <v>0.4920442711405158</v>
+        <v>0.4920442711405159</v>
       </c>
       <c r="X398" t="n">
-        <v>0.5079557288594843</v>
+        <v>0.507955728859484</v>
       </c>
       <c r="Y398" t="n">
         <v>1.57</v>
@@ -55272,7 +55272,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B399" t="n">
         <v>390</v>
@@ -55307,7 +55307,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -55321,13 +55321,13 @@
         </is>
       </c>
       <c r="L399" t="n">
-        <v>0.4754403614542098</v>
+        <v>0.6353262209473198</v>
       </c>
       <c r="M399" t="n">
-        <v>0.1433167424138836</v>
+        <v>0.1711855435829157</v>
       </c>
       <c r="N399" t="n">
-        <v>0.3812428961319068</v>
+        <v>0.1934882354697649</v>
       </c>
       <c r="O399" t="n">
         <v>0.05373764801376313</v>
@@ -55408,7 +55408,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B400" t="n">
         <v>390</v>
@@ -55544,7 +55544,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B401" t="n">
         <v>390</v>
@@ -55680,7 +55680,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B402" t="n">
         <v>390</v>
@@ -55816,7 +55816,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B403" t="n">
         <v>390</v>
@@ -55952,7 +55952,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B404" t="n">
         <v>390</v>
@@ -56010,16 +56010,16 @@
         <v>0.1934882354697649</v>
       </c>
       <c r="O404" t="n">
-        <v>0.031490826664206</v>
+        <v>0.03149082666420611</v>
       </c>
       <c r="P404" t="n">
-        <v>0.968509173335794</v>
+        <v>0.9685091733357939</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.2652485056649188</v>
+        <v>0.2652485056649186</v>
       </c>
       <c r="R404" t="n">
-        <v>0.7347514943350812</v>
+        <v>0.7347514943350814</v>
       </c>
       <c r="S404" t="n">
         <v>0.4982202925848063</v>
@@ -56028,16 +56028,16 @@
         <v>0.5017797074151937</v>
       </c>
       <c r="U404" t="n">
-        <v>0.7086189245957712</v>
+        <v>0.7086189245957711</v>
       </c>
       <c r="V404" t="n">
-        <v>0.2913810754042288</v>
+        <v>0.2913810754042289</v>
       </c>
       <c r="W404" t="n">
-        <v>0.5470911664608165</v>
+        <v>0.5470911664608163</v>
       </c>
       <c r="X404" t="n">
-        <v>0.4529088335391835</v>
+        <v>0.4529088335391837</v>
       </c>
       <c r="Y404" t="n">
         <v>1.61</v>
@@ -56088,7 +56088,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B405" t="n">
         <v>390</v>
@@ -56118,12 +56118,12 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Visitante</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -56137,13 +56137,13 @@
         </is>
       </c>
       <c r="L405" t="n">
-        <v>0.2243854660371182</v>
+        <v>0.3678274953893951</v>
       </c>
       <c r="M405" t="n">
-        <v>0.1729616485866504</v>
+        <v>0.2761646625437316</v>
       </c>
       <c r="N405" t="n">
-        <v>0.6026528853762314</v>
+        <v>0.3560078420668735</v>
       </c>
       <c r="O405" t="n">
         <v>0.09564563809742621</v>
@@ -56224,7 +56224,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B406" t="n">
         <v>390</v>
@@ -56360,7 +56360,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B407" t="n">
         <v>390</v>
@@ -56496,7 +56496,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B408" t="n">
         <v>390</v>
@@ -56632,7 +56632,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B409" t="n">
         <v>390</v>
@@ -56768,7 +56768,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B410" t="n">
         <v>390</v>
@@ -56809,31 +56809,31 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="n">
-        <v>0.3678274953893952</v>
+        <v>0.3678274953893951</v>
       </c>
       <c r="M410" t="n">
         <v>0.2761646625437316</v>
       </c>
       <c r="N410" t="n">
-        <v>0.3560078420668732</v>
+        <v>0.3560078420668735</v>
       </c>
       <c r="O410" t="n">
-        <v>0.1306546269481099</v>
+        <v>0.1306546269481101</v>
       </c>
       <c r="P410" t="n">
-        <v>0.8693453730518901</v>
+        <v>0.8693453730518899</v>
       </c>
       <c r="Q410" t="n">
-        <v>0.3877514148942766</v>
+        <v>0.3877514148942764</v>
       </c>
       <c r="R410" t="n">
-        <v>0.6122485851057234</v>
+        <v>0.6122485851057236</v>
       </c>
       <c r="S410" t="n">
-        <v>0.6274450384917455</v>
+        <v>0.6274450384917454</v>
       </c>
       <c r="T410" t="n">
-        <v>0.3725549615082545</v>
+        <v>0.3725549615082546</v>
       </c>
       <c r="U410" t="n">
         <v>0.8337786548610733</v>
@@ -56842,10 +56842,10 @@
         <v>0.1662213451389267</v>
       </c>
       <c r="W410" t="n">
-        <v>0.4427436752676189</v>
+        <v>0.4427436752676187</v>
       </c>
       <c r="X410" t="n">
-        <v>0.5572563247323812</v>
+        <v>0.5572563247323813</v>
       </c>
       <c r="Y410" t="n">
         <v>2.75</v>
@@ -56896,7 +56896,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B411" t="n">
         <v>390</v>
@@ -56945,13 +56945,13 @@
         </is>
       </c>
       <c r="L411" t="n">
-        <v>0.441358442087512</v>
+        <v>0.6290405024071875</v>
       </c>
       <c r="M411" t="n">
-        <v>0.2636707203278639</v>
+        <v>0.1816944810979464</v>
       </c>
       <c r="N411" t="n">
-        <v>0.2949708375846241</v>
+        <v>0.1892650164948664</v>
       </c>
       <c r="O411" t="n">
         <v>0.07656947436946315</v>
@@ -57032,7 +57032,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B412" t="n">
         <v>390</v>
@@ -57168,7 +57168,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B413" t="n">
         <v>390</v>
@@ -57304,7 +57304,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B414" t="n">
         <v>390</v>
@@ -57440,7 +57440,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B415" t="n">
         <v>390</v>
@@ -57576,7 +57576,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.32319444444</v>
       </c>
       <c r="B416" t="n">
         <v>390</v>
@@ -57625,7 +57625,7 @@
         </is>
       </c>
       <c r="L416" t="n">
-        <v>0.6290405024071876</v>
+        <v>0.6290405024071875</v>
       </c>
       <c r="M416" t="n">
         <v>0.1816944810979464</v>
@@ -57634,10 +57634,10 @@
         <v>0.1892650164948664</v>
       </c>
       <c r="O416" t="n">
-        <v>0.03122995870045731</v>
+        <v>0.03122995870045708</v>
       </c>
       <c r="P416" t="n">
-        <v>0.9687700412995427</v>
+        <v>0.9687700412995429</v>
       </c>
       <c r="Q416" t="n">
         <v>0.3242852105707752</v>
@@ -57646,10 +57646,10 @@
         <v>0.6757147894292248</v>
       </c>
       <c r="S416" t="n">
-        <v>0.6268205566972486</v>
+        <v>0.6268205566972485</v>
       </c>
       <c r="T416" t="n">
-        <v>0.3731794433027514</v>
+        <v>0.3731794433027515</v>
       </c>
       <c r="U416" t="n">
         <v>0.8472269609792713</v>
@@ -57658,10 +57658,10 @@
         <v>0.1527730390207287</v>
       </c>
       <c r="W416" t="n">
-        <v>0.5225373595199285</v>
+        <v>0.5225373595199284</v>
       </c>
       <c r="X416" t="n">
-        <v>0.4774626404800715</v>
+        <v>0.4774626404800716</v>
       </c>
       <c r="Y416" t="n">
         <v>1.51</v>

--- a/PrevisaoJogos.xlsx
+++ b/PrevisaoJogos.xlsx
@@ -48808,7 +48808,7 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B351" t="n">
         <v>390</v>
@@ -48863,7 +48863,7 @@
         <v>0.3322993245014851</v>
       </c>
       <c r="N351" t="n">
-        <v>0.3247347485553387</v>
+        <v>0.3247347485553388</v>
       </c>
       <c r="O351" t="n">
         <v>0.1020704514520514</v>
@@ -48944,7 +48944,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B352" t="n">
         <v>390</v>
@@ -49080,7 +49080,7 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B353" t="n">
         <v>390</v>
@@ -49216,7 +49216,7 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B354" t="n">
         <v>390</v>
@@ -49344,7 +49344,7 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B355" t="n">
         <v>390</v>
@@ -49374,7 +49374,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Empate</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49393,37 +49393,37 @@
         </is>
       </c>
       <c r="L355" t="n">
-        <v>0.1965094526705545</v>
+        <v>0.2415293727085439</v>
       </c>
       <c r="M355" t="n">
-        <v>0.4631463312096707</v>
+        <v>0.3183811736902235</v>
       </c>
       <c r="N355" t="n">
-        <v>0.3403442161197748</v>
+        <v>0.4400894536012325</v>
       </c>
       <c r="O355" t="n">
-        <v>0.05251547132252699</v>
+        <v>0.1842756431078284</v>
       </c>
       <c r="P355" t="n">
-        <v>0.947484528677473</v>
+        <v>0.8157243568921716</v>
       </c>
       <c r="Q355" t="n">
-        <v>0.6796040613289052</v>
+        <v>0.4786376418071928</v>
       </c>
       <c r="R355" t="n">
-        <v>0.3203959386710949</v>
+        <v>0.5213623581928072</v>
       </c>
       <c r="S355" t="n">
-        <v>0.7482550868651852</v>
+        <v>0.5782145137592576</v>
       </c>
       <c r="T355" t="n">
-        <v>0.2517449131348149</v>
+        <v>0.4217854862407425</v>
       </c>
       <c r="U355" t="n">
-        <v>0.7482550868651852</v>
+        <v>0.6031700210877029</v>
       </c>
       <c r="V355" t="n">
-        <v>0.2517449131348149</v>
+        <v>0.3968299789122972</v>
       </c>
       <c r="W355" t="n">
         <v>0.4986618098798136</v>
@@ -49480,7 +49480,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B356" t="n">
         <v>390</v>
@@ -49535,7 +49535,7 @@
         <v>0.3322993245014851</v>
       </c>
       <c r="N356" t="n">
-        <v>0.3247347485553387</v>
+        <v>0.3247347485553388</v>
       </c>
       <c r="O356" t="n">
         <v>0.1594213890890545</v>
@@ -49544,16 +49544,16 @@
         <v>0.8405786109109455</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.3438578129164603</v>
+        <v>0.3438578129164604</v>
       </c>
       <c r="R356" t="n">
-        <v>0.6561421870835397</v>
+        <v>0.6561421870835396</v>
       </c>
       <c r="S356" t="n">
         <v>0.6069396571986343</v>
       </c>
       <c r="T356" t="n">
-        <v>0.3930603428013657</v>
+        <v>0.3930603428013658</v>
       </c>
       <c r="U356" t="n">
         <v>0.7901421824726422</v>
@@ -49616,7 +49616,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B357" t="n">
         <v>325</v>
@@ -49752,7 +49752,7 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B358" t="n">
         <v>325</v>
@@ -49888,7 +49888,7 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B359" t="n">
         <v>325</v>
@@ -50024,7 +50024,7 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B360" t="n">
         <v>325</v>
@@ -50160,7 +50160,7 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B361" t="n">
         <v>325</v>
@@ -50201,37 +50201,37 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="n">
-        <v>0.7006899175767403</v>
+        <v>0.4932693171585404</v>
       </c>
       <c r="M361" t="n">
-        <v>0.2159490784299468</v>
+        <v>0.2965811130252543</v>
       </c>
       <c r="N361" t="n">
-        <v>0.08336100399331298</v>
+        <v>0.2101495698162055</v>
       </c>
       <c r="O361" t="n">
-        <v>0.000306409917731898</v>
+        <v>0.01057292927854558</v>
       </c>
       <c r="P361" t="n">
-        <v>0.9996935900822681</v>
+        <v>0.9894270707214544</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.03248379756796649</v>
+        <v>0.03695055440952266</v>
       </c>
       <c r="R361" t="n">
-        <v>0.9675162024320335</v>
+        <v>0.9630494455904773</v>
       </c>
       <c r="S361" t="n">
-        <v>0.2077799100774491</v>
+        <v>0.1943850425090896</v>
       </c>
       <c r="T361" t="n">
-        <v>0.7922200899225509</v>
+        <v>0.8056149574909104</v>
       </c>
       <c r="U361" t="n">
-        <v>0.2077799100774491</v>
+        <v>0.1943850425090896</v>
       </c>
       <c r="V361" t="n">
-        <v>0.7922200899225509</v>
+        <v>0.8056149574909104</v>
       </c>
       <c r="W361" t="n">
         <v>0.3878158776577057</v>
@@ -50288,7 +50288,7 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>45940.49365740741</v>
+        <v>45941.41020833333</v>
       </c>
       <c r="B362" t="n">
         <v>325</v>
@@ -50329,10 +50329,10 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="n">
-        <v>0.6506919052177619</v>
+        <v>0.6506919052177617</v>
       </c>
       <c r="M362" t="n">
-        <v>0.2452004030999282</v>
+        <v>0.2452004030999281</v>
       </c>
       <c r="N362" t="n">
         <v>0.1041076916823105</v>
@@ -50344,28 +50344,28 @@
         <v>0.7551702112908434</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.3283895870013728</v>
+        <v>0.3283895870013729</v>
       </c>
       <c r="R362" t="n">
-        <v>0.6716104129986272</v>
+        <v>0.6716104129986271</v>
       </c>
       <c r="S362" t="n">
         <v>0.5482265833447206</v>
       </c>
       <c r="T362" t="n">
-        <v>0.4517734166552794</v>
+        <v>0.4517734166552793</v>
       </c>
       <c r="U362" t="n">
         <v>0.607249393639822</v>
       </c>
       <c r="V362" t="n">
-        <v>0.3927506063601779</v>
+        <v>0.392750606360178</v>
       </c>
       <c r="W362" t="n">
-        <v>0.4158445681314064</v>
+        <v>0.4158445681314063</v>
       </c>
       <c r="X362" t="n">
-        <v>0.5841554318685936</v>
+        <v>0.5841554318685938</v>
       </c>
       <c r="Y362" t="n">
         <v>1.22</v>
@@ -50416,7 +50416,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B363" t="n">
         <v>390</v>
@@ -50552,7 +50552,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B364" t="n">
         <v>390</v>
@@ -50688,7 +50688,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B365" t="n">
         <v>390</v>
@@ -50824,7 +50824,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B366" t="n">
         <v>390</v>
@@ -50960,7 +50960,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B367" t="n">
         <v>390</v>
@@ -50990,7 +50990,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -51009,37 +51009,37 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>0.4428379900159204</v>
+        <v>0.323656760586769</v>
       </c>
       <c r="M367" t="n">
-        <v>0.2653447035741059</v>
+        <v>0.2737723242236736</v>
       </c>
       <c r="N367" t="n">
-        <v>0.2918173064099738</v>
+        <v>0.4025709151895573</v>
       </c>
       <c r="O367" t="n">
-        <v>0.003232437655791287</v>
+        <v>0.02450983897607906</v>
       </c>
       <c r="P367" t="n">
-        <v>0.9967675623442087</v>
+        <v>0.9754901610239209</v>
       </c>
       <c r="Q367" t="n">
-        <v>0.4301548701535519</v>
+        <v>0.6028685856147913</v>
       </c>
       <c r="R367" t="n">
-        <v>0.5698451298464481</v>
+        <v>0.3971314143852087</v>
       </c>
       <c r="S367" t="n">
-        <v>0.4496811005995853</v>
+        <v>0.8261371118502276</v>
       </c>
       <c r="T367" t="n">
-        <v>0.5503188994004147</v>
+        <v>0.1738628881497724</v>
       </c>
       <c r="U367" t="n">
-        <v>0.9821677799462648</v>
+        <v>0.8261371118502276</v>
       </c>
       <c r="V367" t="n">
-        <v>0.01783222005373523</v>
+        <v>0.1738628881497724</v>
       </c>
       <c r="W367" t="n">
         <v>0.4196558708594321</v>
@@ -51096,7 +51096,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B368" t="n">
         <v>390</v>
@@ -51160,16 +51160,16 @@
         <v>0.9061315980599771</v>
       </c>
       <c r="Q368" t="n">
-        <v>0.2907946001345738</v>
+        <v>0.2907946001345737</v>
       </c>
       <c r="R368" t="n">
-        <v>0.7092053998654262</v>
+        <v>0.7092053998654263</v>
       </c>
       <c r="S368" t="n">
-        <v>0.5601939395715148</v>
+        <v>0.5601939395715149</v>
       </c>
       <c r="T368" t="n">
-        <v>0.4398060604284852</v>
+        <v>0.4398060604284851</v>
       </c>
       <c r="U368" t="n">
         <v>0.8389483496533513</v>
@@ -51232,7 +51232,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B369" t="n">
         <v>390</v>
@@ -51281,13 +51281,13 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>0.5032479285748984</v>
+        <v>0.5032479285748983</v>
       </c>
       <c r="M369" t="n">
         <v>0.313933159221518</v>
       </c>
       <c r="N369" t="n">
-        <v>0.1828189122035836</v>
+        <v>0.1828189122035837</v>
       </c>
       <c r="O369" t="n">
         <v>0.06102815402948403</v>
@@ -51368,7 +51368,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B370" t="n">
         <v>390</v>
@@ -51504,7 +51504,7 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B371" t="n">
         <v>390</v>
@@ -51640,7 +51640,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B372" t="n">
         <v>390</v>
@@ -51768,7 +51768,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B373" t="n">
         <v>390</v>
@@ -51798,7 +51798,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51809,37 +51809,37 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="n">
-        <v>0.4616914748756129</v>
+        <v>0.3241951754490096</v>
       </c>
       <c r="M373" t="n">
-        <v>0.2792795875201975</v>
+        <v>0.31854179091832</v>
       </c>
       <c r="N373" t="n">
-        <v>0.2590289376041895</v>
+        <v>0.3572630336326703</v>
       </c>
       <c r="O373" t="n">
-        <v>0.004795922293999499</v>
+        <v>0.1390367946193941</v>
       </c>
       <c r="P373" t="n">
-        <v>0.9952040777060005</v>
+        <v>0.8609632053806059</v>
       </c>
       <c r="Q373" t="n">
-        <v>0.3984041314483312</v>
+        <v>0.4172926237034689</v>
       </c>
       <c r="R373" t="n">
-        <v>0.6015958685516688</v>
+        <v>0.5827073762965311</v>
       </c>
       <c r="S373" t="n">
-        <v>0.6538894348880804</v>
+        <v>0.6816275360999706</v>
       </c>
       <c r="T373" t="n">
-        <v>0.3461105651119196</v>
+        <v>0.3183724639000294</v>
       </c>
       <c r="U373" t="n">
-        <v>0.9732498109712574</v>
+        <v>0.6816275360999706</v>
       </c>
       <c r="V373" t="n">
-        <v>0.02675018902874263</v>
+        <v>0.3183724639000294</v>
       </c>
       <c r="W373" t="n">
         <v>0.3853052279019517</v>
@@ -51896,7 +51896,7 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B374" t="n">
         <v>390</v>
@@ -51937,28 +51937,28 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="n">
-        <v>0.5032479285748984</v>
+        <v>0.5032479285748983</v>
       </c>
       <c r="M374" t="n">
         <v>0.313933159221518</v>
       </c>
       <c r="N374" t="n">
-        <v>0.1828189122035836</v>
+        <v>0.1828189122035837</v>
       </c>
       <c r="O374" t="n">
-        <v>0.03290281907865722</v>
+        <v>0.03290281907865744</v>
       </c>
       <c r="P374" t="n">
-        <v>0.9670971809213428</v>
+        <v>0.9670971809213426</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.368586231980446</v>
+        <v>0.3685862319804458</v>
       </c>
       <c r="R374" t="n">
-        <v>0.631413768019554</v>
+        <v>0.6314137680195542</v>
       </c>
       <c r="S374" t="n">
-        <v>0.5982532627776024</v>
+        <v>0.5982532627776025</v>
       </c>
       <c r="T374" t="n">
         <v>0.4017467372223976</v>
@@ -51970,10 +51970,10 @@
         <v>0.1726033420691784</v>
       </c>
       <c r="W374" t="n">
-        <v>0.5515892768954774</v>
+        <v>0.5515892768954773</v>
       </c>
       <c r="X374" t="n">
-        <v>0.4484107231045226</v>
+        <v>0.4484107231045227</v>
       </c>
       <c r="Y374" t="n">
         <v>1.91</v>
@@ -52024,7 +52024,7 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B375" t="n">
         <v>390</v>
@@ -52073,7 +52073,7 @@
         </is>
       </c>
       <c r="L375" t="n">
-        <v>0.4297381803308904</v>
+        <v>0.4297381803308905</v>
       </c>
       <c r="M375" t="n">
         <v>0.3372471649105065</v>
@@ -52160,7 +52160,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B376" t="n">
         <v>390</v>
@@ -52296,7 +52296,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B377" t="n">
         <v>390</v>
@@ -52432,7 +52432,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B378" t="n">
         <v>390</v>
@@ -52568,7 +52568,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B379" t="n">
         <v>390</v>
@@ -52617,37 +52617,37 @@
         </is>
       </c>
       <c r="L379" t="n">
-        <v>0.485421571044561</v>
+        <v>0.5992251828237452</v>
       </c>
       <c r="M379" t="n">
-        <v>0.2363429846823315</v>
+        <v>0.2976119990642267</v>
       </c>
       <c r="N379" t="n">
-        <v>0.2782354442731076</v>
+        <v>0.1031628181120281</v>
       </c>
       <c r="O379" t="n">
-        <v>0.004990255960187318</v>
+        <v>0.08513950050974617</v>
       </c>
       <c r="P379" t="n">
-        <v>0.9950097440398127</v>
+        <v>0.9148604994902538</v>
       </c>
       <c r="Q379" t="n">
-        <v>0.2997693242697942</v>
+        <v>0.5938256778855144</v>
       </c>
       <c r="R379" t="n">
-        <v>0.7002306757302058</v>
+        <v>0.4061743221144856</v>
       </c>
       <c r="S379" t="n">
-        <v>0.8389938876246106</v>
+        <v>0.6817451804526</v>
       </c>
       <c r="T379" t="n">
-        <v>0.1610061123753895</v>
+        <v>0.3182548195473999</v>
       </c>
       <c r="U379" t="n">
-        <v>0.8389938876246106</v>
+        <v>0.6817451804526</v>
       </c>
       <c r="V379" t="n">
-        <v>0.1610061123753895</v>
+        <v>0.3182548195473999</v>
       </c>
       <c r="W379" t="n">
         <v>0.4461624265203107</v>
@@ -52704,7 +52704,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B380" t="n">
         <v>390</v>
@@ -52753,7 +52753,7 @@
         </is>
       </c>
       <c r="L380" t="n">
-        <v>0.4297381803308904</v>
+        <v>0.4297381803308905</v>
       </c>
       <c r="M380" t="n">
         <v>0.3372471649105065</v>
@@ -52762,25 +52762,25 @@
         <v>0.2330146547586029</v>
       </c>
       <c r="O380" t="n">
-        <v>0.06509688016033399</v>
+        <v>0.06509688016033377</v>
       </c>
       <c r="P380" t="n">
-        <v>0.934903119839666</v>
+        <v>0.9349031198396662</v>
       </c>
       <c r="Q380" t="n">
-        <v>0.2903066358449776</v>
+        <v>0.2903066358449775</v>
       </c>
       <c r="R380" t="n">
-        <v>0.7096933641550224</v>
+        <v>0.7096933641550225</v>
       </c>
       <c r="S380" t="n">
-        <v>0.64783451056643</v>
+        <v>0.6478345105664302</v>
       </c>
       <c r="T380" t="n">
-        <v>0.3521654894335699</v>
+        <v>0.3521654894335698</v>
       </c>
       <c r="U380" t="n">
-        <v>0.7887373925621955</v>
+        <v>0.7887373925621957</v>
       </c>
       <c r="V380" t="n">
         <v>0.2112626074378044</v>
@@ -52840,7 +52840,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B381" t="n">
         <v>390</v>
@@ -52889,10 +52889,10 @@
         </is>
       </c>
       <c r="L381" t="n">
-        <v>0.4134723763376076</v>
+        <v>0.4134723763376075</v>
       </c>
       <c r="M381" t="n">
-        <v>0.2757685288000669</v>
+        <v>0.275768528800067</v>
       </c>
       <c r="N381" t="n">
         <v>0.3107590948623259</v>
@@ -52976,7 +52976,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B382" t="n">
         <v>390</v>
@@ -53112,7 +53112,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B383" t="n">
         <v>390</v>
@@ -53240,7 +53240,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B384" t="n">
         <v>390</v>
@@ -53376,7 +53376,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B385" t="n">
         <v>390</v>
@@ -53406,7 +53406,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Empate</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53425,37 +53425,37 @@
         </is>
       </c>
       <c r="L385" t="n">
-        <v>0.3640557436140898</v>
+        <v>0.2722715438961565</v>
       </c>
       <c r="M385" t="n">
-        <v>0.3555713209480818</v>
+        <v>0.4901775317596897</v>
       </c>
       <c r="N385" t="n">
-        <v>0.2803729354378284</v>
+        <v>0.2375509243441538</v>
       </c>
       <c r="O385" t="n">
-        <v>0.9202681701717582</v>
+        <v>0.7159104374097646</v>
       </c>
       <c r="P385" t="n">
-        <v>0.07973182982824176</v>
+        <v>0.2840895625902354</v>
       </c>
       <c r="Q385" t="n">
-        <v>0.9202681701717582</v>
+        <v>0.7159104374097646</v>
       </c>
       <c r="R385" t="n">
-        <v>0.07973182982824176</v>
+        <v>0.2840895625902354</v>
       </c>
       <c r="S385" t="n">
-        <v>0.9202681701717582</v>
+        <v>0.7159104374097646</v>
       </c>
       <c r="T385" t="n">
-        <v>0.07973182982824176</v>
+        <v>0.2840895625902354</v>
       </c>
       <c r="U385" t="n">
-        <v>0.9202681701717582</v>
+        <v>0.7159104374097646</v>
       </c>
       <c r="V385" t="n">
-        <v>0.07973182982824176</v>
+        <v>0.2840895625902354</v>
       </c>
       <c r="W385" t="n">
         <v>0.4132478240061758</v>
@@ -53512,7 +53512,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B386" t="n">
         <v>390</v>
@@ -53561,25 +53561,25 @@
         </is>
       </c>
       <c r="L386" t="n">
-        <v>0.4134723763376076</v>
+        <v>0.4134723763376075</v>
       </c>
       <c r="M386" t="n">
-        <v>0.2757685288000669</v>
+        <v>0.275768528800067</v>
       </c>
       <c r="N386" t="n">
         <v>0.3107590948623259</v>
       </c>
       <c r="O386" t="n">
-        <v>0.07404933541947833</v>
+        <v>0.07404933541947822</v>
       </c>
       <c r="P386" t="n">
-        <v>0.9259506645805217</v>
+        <v>0.9259506645805218</v>
       </c>
       <c r="Q386" t="n">
-        <v>0.3812790268066503</v>
+        <v>0.38127902680665</v>
       </c>
       <c r="R386" t="n">
-        <v>0.6187209731933497</v>
+        <v>0.61872097319335</v>
       </c>
       <c r="S386" t="n">
         <v>0.7120694267462797</v>
@@ -53594,10 +53594,10 @@
         <v>0.1131477015540442</v>
       </c>
       <c r="W386" t="n">
-        <v>0.4443253995655359</v>
+        <v>0.444325399565536</v>
       </c>
       <c r="X386" t="n">
-        <v>0.5556746004344641</v>
+        <v>0.555674600434464</v>
       </c>
       <c r="Y386" t="n">
         <v>2.3</v>
@@ -53648,7 +53648,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B387" t="n">
         <v>390</v>
@@ -53784,7 +53784,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B388" t="n">
         <v>390</v>
@@ -53920,7 +53920,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B389" t="n">
         <v>390</v>
@@ -54056,7 +54056,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B390" t="n">
         <v>390</v>
@@ -54192,7 +54192,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B391" t="n">
         <v>390</v>
@@ -54222,7 +54222,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Empate</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -54241,37 +54241,37 @@
         </is>
       </c>
       <c r="L391" t="n">
-        <v>0.1637225949241595</v>
+        <v>0.1382866150333152</v>
       </c>
       <c r="M391" t="n">
-        <v>0.4247522863571578</v>
+        <v>0.3421051424874755</v>
       </c>
       <c r="N391" t="n">
-        <v>0.4115251187186826</v>
+        <v>0.5196082424792093</v>
       </c>
       <c r="O391" t="n">
-        <v>0.4212845303643652</v>
+        <v>0.6476089179404689</v>
       </c>
       <c r="P391" t="n">
-        <v>0.5787154696356348</v>
+        <v>0.352391082059531</v>
       </c>
       <c r="Q391" t="n">
-        <v>0.4792543617295318</v>
+        <v>0.6476089179404689</v>
       </c>
       <c r="R391" t="n">
-        <v>0.5207456382704682</v>
+        <v>0.352391082059531</v>
       </c>
       <c r="S391" t="n">
-        <v>0.4792543617295318</v>
+        <v>0.7309942490544102</v>
       </c>
       <c r="T391" t="n">
-        <v>0.5207456382704682</v>
+        <v>0.2690057509455898</v>
       </c>
       <c r="U391" t="n">
-        <v>0.5389337724577163</v>
+        <v>0.7309942490544102</v>
       </c>
       <c r="V391" t="n">
-        <v>0.4610662275422837</v>
+        <v>0.2690057509455898</v>
       </c>
       <c r="W391" t="n">
         <v>0.4932836862596571</v>
@@ -54328,7 +54328,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B392" t="n">
         <v>390</v>
@@ -54384,16 +54384,16 @@
         <v>0.8555519172541893</v>
       </c>
       <c r="Q392" t="n">
-        <v>0.3989284122995039</v>
+        <v>0.3989284122995036</v>
       </c>
       <c r="R392" t="n">
-        <v>0.6010715877004961</v>
+        <v>0.6010715877004964</v>
       </c>
       <c r="S392" t="n">
         <v>0.593455876156892</v>
       </c>
       <c r="T392" t="n">
-        <v>0.406544123843108</v>
+        <v>0.4065441238431081</v>
       </c>
       <c r="U392" t="n">
         <v>0.8502505954061139</v>
@@ -54402,10 +54402,10 @@
         <v>0.1497494045938861</v>
       </c>
       <c r="W392" t="n">
-        <v>0.4373463133143934</v>
+        <v>0.4373463133143935</v>
       </c>
       <c r="X392" t="n">
-        <v>0.5626536866856067</v>
+        <v>0.5626536866856064</v>
       </c>
       <c r="Y392" t="n">
         <v>2.5</v>
@@ -54456,7 +54456,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B393" t="n">
         <v>390</v>
@@ -54505,7 +54505,7 @@
         </is>
       </c>
       <c r="L393" t="n">
-        <v>0.5792133233484628</v>
+        <v>0.5792133233484626</v>
       </c>
       <c r="M393" t="n">
         <v>0.2324624955755505</v>
@@ -54592,7 +54592,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B394" t="n">
         <v>390</v>
@@ -54728,7 +54728,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B395" t="n">
         <v>390</v>
@@ -54864,7 +54864,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B396" t="n">
         <v>390</v>
@@ -55000,7 +55000,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B397" t="n">
         <v>390</v>
@@ -55030,7 +55030,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Empate</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -55049,37 +55049,37 @@
         </is>
       </c>
       <c r="L397" t="n">
-        <v>0.3231312558118901</v>
+        <v>0.4417684463983721</v>
       </c>
       <c r="M397" t="n">
-        <v>0.3414095354614936</v>
+        <v>0.4133142049142866</v>
       </c>
       <c r="N397" t="n">
-        <v>0.3354592087266164</v>
+        <v>0.1449173486873412</v>
       </c>
       <c r="O397" t="n">
-        <v>0.0005188841153550561</v>
+        <v>0.06102866169449284</v>
       </c>
       <c r="P397" t="n">
-        <v>0.9994811158846449</v>
+        <v>0.9389713383055072</v>
       </c>
       <c r="Q397" t="n">
-        <v>0.4503658690647233</v>
+        <v>0.6400233215550244</v>
       </c>
       <c r="R397" t="n">
-        <v>0.5496341309352767</v>
+        <v>0.3599766784449756</v>
       </c>
       <c r="S397" t="n">
-        <v>0.7118649944680954</v>
+        <v>0.8532468883363664</v>
       </c>
       <c r="T397" t="n">
-        <v>0.2881350055319046</v>
+        <v>0.1467531116636336</v>
       </c>
       <c r="U397" t="n">
-        <v>0.8791776967301904</v>
+        <v>0.8532468883363664</v>
       </c>
       <c r="V397" t="n">
-        <v>0.1208223032698095</v>
+        <v>0.1467531116636336</v>
       </c>
       <c r="W397" t="n">
         <v>0.3135088701228894</v>
@@ -55136,7 +55136,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B398" t="n">
         <v>390</v>
@@ -55185,7 +55185,7 @@
         </is>
       </c>
       <c r="L398" t="n">
-        <v>0.5792133233484628</v>
+        <v>0.5792133233484626</v>
       </c>
       <c r="M398" t="n">
         <v>0.2324624955755505</v>
@@ -55200,16 +55200,16 @@
         <v>0.9455440888786811</v>
       </c>
       <c r="Q398" t="n">
-        <v>0.325864948234457</v>
+        <v>0.3258649482344572</v>
       </c>
       <c r="R398" t="n">
-        <v>0.674135051765543</v>
+        <v>0.6741350517655428</v>
       </c>
       <c r="S398" t="n">
-        <v>0.4946378891932037</v>
+        <v>0.4946378891932036</v>
       </c>
       <c r="T398" t="n">
-        <v>0.5053621108067963</v>
+        <v>0.5053621108067964</v>
       </c>
       <c r="U398" t="n">
         <v>0.7668028445175321</v>
@@ -55218,7 +55218,7 @@
         <v>0.2331971554824679</v>
       </c>
       <c r="W398" t="n">
-        <v>0.4920442711405159</v>
+        <v>0.492044271140516</v>
       </c>
       <c r="X398" t="n">
         <v>0.507955728859484</v>
@@ -55272,7 +55272,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B399" t="n">
         <v>390</v>
@@ -55321,7 +55321,7 @@
         </is>
       </c>
       <c r="L399" t="n">
-        <v>0.6353262209473198</v>
+        <v>0.6353262209473196</v>
       </c>
       <c r="M399" t="n">
         <v>0.1711855435829157</v>
@@ -55408,7 +55408,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B400" t="n">
         <v>390</v>
@@ -55544,7 +55544,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B401" t="n">
         <v>390</v>
@@ -55680,7 +55680,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B402" t="n">
         <v>390</v>
@@ -55816,7 +55816,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B403" t="n">
         <v>390</v>
@@ -55846,7 +55846,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Visitante</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -55865,37 +55865,37 @@
         </is>
       </c>
       <c r="L403" t="n">
-        <v>0.4771879435547778</v>
+        <v>0.3106775428709934</v>
       </c>
       <c r="M403" t="n">
-        <v>0.2174498039103327</v>
+        <v>0.3289289777018282</v>
       </c>
       <c r="N403" t="n">
-        <v>0.3053622525348895</v>
+        <v>0.3603934794271784</v>
       </c>
       <c r="O403" t="n">
-        <v>0.0002505257367491076</v>
+        <v>0.01067702584496799</v>
       </c>
       <c r="P403" t="n">
-        <v>0.9997494742632509</v>
+        <v>0.989322974155032</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.1873130426539031</v>
+        <v>0.2796422264418078</v>
       </c>
       <c r="R403" t="n">
-        <v>0.8126869573460969</v>
+        <v>0.7203577735581922</v>
       </c>
       <c r="S403" t="n">
-        <v>0.4141341566764984</v>
+        <v>0.6081057640489809</v>
       </c>
       <c r="T403" t="n">
-        <v>0.5858658433235016</v>
+        <v>0.3918942359510192</v>
       </c>
       <c r="U403" t="n">
-        <v>0.4141341566764984</v>
+        <v>0.6081057640489809</v>
       </c>
       <c r="V403" t="n">
-        <v>0.5858658433235016</v>
+        <v>0.3918942359510192</v>
       </c>
       <c r="W403" t="n">
         <v>0.6606033681862746</v>
@@ -55952,7 +55952,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B404" t="n">
         <v>390</v>
@@ -56001,7 +56001,7 @@
         </is>
       </c>
       <c r="L404" t="n">
-        <v>0.6353262209473198</v>
+        <v>0.6353262209473196</v>
       </c>
       <c r="M404" t="n">
         <v>0.1711855435829157</v>
@@ -56010,10 +56010,10 @@
         <v>0.1934882354697649</v>
       </c>
       <c r="O404" t="n">
-        <v>0.03149082666420611</v>
+        <v>0.03149082666420633</v>
       </c>
       <c r="P404" t="n">
-        <v>0.9685091733357939</v>
+        <v>0.9685091733357937</v>
       </c>
       <c r="Q404" t="n">
         <v>0.2652485056649186</v>
@@ -56022,22 +56022,22 @@
         <v>0.7347514943350814</v>
       </c>
       <c r="S404" t="n">
-        <v>0.4982202925848063</v>
+        <v>0.4982202925848064</v>
       </c>
       <c r="T404" t="n">
-        <v>0.5017797074151937</v>
+        <v>0.5017797074151936</v>
       </c>
       <c r="U404" t="n">
-        <v>0.7086189245957711</v>
+        <v>0.7086189245957712</v>
       </c>
       <c r="V404" t="n">
-        <v>0.2913810754042289</v>
+        <v>0.2913810754042287</v>
       </c>
       <c r="W404" t="n">
-        <v>0.5470911664608163</v>
+        <v>0.5470911664608165</v>
       </c>
       <c r="X404" t="n">
-        <v>0.4529088335391837</v>
+        <v>0.4529088335391835</v>
       </c>
       <c r="Y404" t="n">
         <v>1.61</v>
@@ -56088,7 +56088,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B405" t="n">
         <v>390</v>
@@ -56143,7 +56143,7 @@
         <v>0.2761646625437316</v>
       </c>
       <c r="N405" t="n">
-        <v>0.3560078420668735</v>
+        <v>0.3560078420668734</v>
       </c>
       <c r="O405" t="n">
         <v>0.09564563809742621</v>
@@ -56224,7 +56224,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B406" t="n">
         <v>390</v>
@@ -56360,7 +56360,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B407" t="n">
         <v>390</v>
@@ -56496,7 +56496,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B408" t="n">
         <v>390</v>
@@ -56632,7 +56632,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B409" t="n">
         <v>390</v>
@@ -56662,7 +56662,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Visitante</t>
+          <t>Empate</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -56681,37 +56681,37 @@
         </is>
       </c>
       <c r="L409" t="n">
-        <v>0.2428443633364521</v>
+        <v>0.3671384271254608</v>
       </c>
       <c r="M409" t="n">
-        <v>0.2837601045959024</v>
+        <v>0.3716801510431477</v>
       </c>
       <c r="N409" t="n">
-        <v>0.4733955320676456</v>
+        <v>0.2611814218313915</v>
       </c>
       <c r="O409" t="n">
-        <v>0.0657333355260652</v>
+        <v>0.1667266378889023</v>
       </c>
       <c r="P409" t="n">
-        <v>0.9342666644739348</v>
+        <v>0.8332733621110977</v>
       </c>
       <c r="Q409" t="n">
-        <v>0.4087868174737017</v>
+        <v>0.4069452426281472</v>
       </c>
       <c r="R409" t="n">
-        <v>0.5912131825262983</v>
+        <v>0.5930547573718528</v>
       </c>
       <c r="S409" t="n">
-        <v>0.4087868174737017</v>
+        <v>0.6069166891241684</v>
       </c>
       <c r="T409" t="n">
-        <v>0.5912131825262983</v>
+        <v>0.3930833108758316</v>
       </c>
       <c r="U409" t="n">
-        <v>0.8074311353743137</v>
+        <v>0.6069166891241684</v>
       </c>
       <c r="V409" t="n">
-        <v>0.1925688646256863</v>
+        <v>0.3930833108758316</v>
       </c>
       <c r="W409" t="n">
         <v>0.2140276918099504</v>
@@ -56768,7 +56768,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B410" t="n">
         <v>390</v>
@@ -56815,13 +56815,13 @@
         <v>0.2761646625437316</v>
       </c>
       <c r="N410" t="n">
-        <v>0.3560078420668735</v>
+        <v>0.3560078420668734</v>
       </c>
       <c r="O410" t="n">
-        <v>0.1306546269481101</v>
+        <v>0.13065462694811</v>
       </c>
       <c r="P410" t="n">
-        <v>0.8693453730518899</v>
+        <v>0.86934537305189</v>
       </c>
       <c r="Q410" t="n">
         <v>0.3877514148942764</v>
@@ -56839,13 +56839,13 @@
         <v>0.8337786548610733</v>
       </c>
       <c r="V410" t="n">
-        <v>0.1662213451389267</v>
+        <v>0.1662213451389268</v>
       </c>
       <c r="W410" t="n">
-        <v>0.4427436752676187</v>
+        <v>0.4427436752676188</v>
       </c>
       <c r="X410" t="n">
-        <v>0.5572563247323813</v>
+        <v>0.5572563247323812</v>
       </c>
       <c r="Y410" t="n">
         <v>2.75</v>
@@ -56896,7 +56896,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B411" t="n">
         <v>390</v>
@@ -56945,13 +56945,13 @@
         </is>
       </c>
       <c r="L411" t="n">
-        <v>0.6290405024071875</v>
+        <v>0.6290405024071871</v>
       </c>
       <c r="M411" t="n">
         <v>0.1816944810979464</v>
       </c>
       <c r="N411" t="n">
-        <v>0.1892650164948664</v>
+        <v>0.1892650164948663</v>
       </c>
       <c r="O411" t="n">
         <v>0.07656947436946315</v>
@@ -57032,7 +57032,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B412" t="n">
         <v>390</v>
@@ -57168,7 +57168,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B413" t="n">
         <v>390</v>
@@ -57304,7 +57304,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B414" t="n">
         <v>390</v>
@@ -57440,7 +57440,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B415" t="n">
         <v>390</v>
@@ -57489,37 +57489,37 @@
         </is>
       </c>
       <c r="L415" t="n">
-        <v>0.4583975138138687</v>
+        <v>0.5311115231035207</v>
       </c>
       <c r="M415" t="n">
-        <v>0.2406932874630696</v>
+        <v>0.1936160636037748</v>
       </c>
       <c r="N415" t="n">
-        <v>0.3009091987230618</v>
+        <v>0.2752724132927044</v>
       </c>
       <c r="O415" t="n">
-        <v>0.07801414362070147</v>
+        <v>0.2605314423087598</v>
       </c>
       <c r="P415" t="n">
-        <v>0.9219858563792985</v>
+        <v>0.7394685576912402</v>
       </c>
       <c r="Q415" t="n">
-        <v>0.5482768000358502</v>
+        <v>0.5276885091107211</v>
       </c>
       <c r="R415" t="n">
-        <v>0.4517231999641498</v>
+        <v>0.4723114908892789</v>
       </c>
       <c r="S415" t="n">
-        <v>0.5482768000358502</v>
+        <v>0.7098087356681022</v>
       </c>
       <c r="T415" t="n">
-        <v>0.4517231999641498</v>
+        <v>0.2901912643318978</v>
       </c>
       <c r="U415" t="n">
-        <v>0.9326106641489759</v>
+        <v>0.7098087356681022</v>
       </c>
       <c r="V415" t="n">
-        <v>0.06738933585102409</v>
+        <v>0.2901912643318978</v>
       </c>
       <c r="W415" t="n">
         <v>0.24834187247593</v>
@@ -57576,7 +57576,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>45941.32319444444</v>
+        <v>45941.40982638889</v>
       </c>
       <c r="B416" t="n">
         <v>390</v>
@@ -57625,31 +57625,31 @@
         </is>
       </c>
       <c r="L416" t="n">
-        <v>0.6290405024071875</v>
+        <v>0.6290405024071871</v>
       </c>
       <c r="M416" t="n">
         <v>0.1816944810979464</v>
       </c>
       <c r="N416" t="n">
-        <v>0.1892650164948664</v>
+        <v>0.1892650164948663</v>
       </c>
       <c r="O416" t="n">
-        <v>0.03122995870045708</v>
+        <v>0.03122995870045719</v>
       </c>
       <c r="P416" t="n">
-        <v>0.9687700412995429</v>
+        <v>0.9687700412995428</v>
       </c>
       <c r="Q416" t="n">
-        <v>0.3242852105707752</v>
+        <v>0.324285210570775</v>
       </c>
       <c r="R416" t="n">
-        <v>0.6757147894292248</v>
+        <v>0.675714789429225</v>
       </c>
       <c r="S416" t="n">
-        <v>0.6268205566972485</v>
+        <v>0.6268205566972486</v>
       </c>
       <c r="T416" t="n">
-        <v>0.3731794433027515</v>
+        <v>0.3731794433027514</v>
       </c>
       <c r="U416" t="n">
         <v>0.8472269609792713</v>
